--- a/docs/data-seed.xlsx
+++ b/docs/data-seed.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\urang\Documents\My_Data\Development\real-project\main\muhsinapp\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6BCF4E9-8D35-4D1C-9323-5D4C3881A0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{849639D7-57B6-4663-B464-9862972736AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{A2928741-0694-43B3-AD53-D76C3E73746F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A2928741-0694-43B3-AD53-D76C3E73746F}"/>
   </bookViews>
   <sheets>
     <sheet name="raw" sheetId="2" r:id="rId1"/>
-    <sheet name="student-class-teacher" sheetId="1" r:id="rId2"/>
+    <sheet name="student-parent-class-teacher" sheetId="1" r:id="rId2"/>
     <sheet name="student" sheetId="5" r:id="rId3"/>
-    <sheet name="teacher" sheetId="3" r:id="rId4"/>
-    <sheet name="class" sheetId="4" r:id="rId5"/>
-    <sheet name="surah" sheetId="6" r:id="rId6"/>
+    <sheet name="parent" sheetId="7" r:id="rId4"/>
+    <sheet name="teacher" sheetId="3" r:id="rId5"/>
+    <sheet name="class" sheetId="4" r:id="rId6"/>
+    <sheet name="surah" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4049" uniqueCount="1123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4053" uniqueCount="1127">
   <si>
     <t>muginayaka@gmail.com</t>
   </si>
@@ -3408,6 +3409,18 @@
   </si>
   <si>
     <t>An Nas</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>student_name</t>
+  </si>
+  <si>
+    <t>parent_name</t>
+  </si>
+  <si>
+    <t>email_parent</t>
   </si>
 </sst>
 </file>
@@ -10227,7 +10240,7 @@
       </c>
       <c r="C257" s="1"/>
       <c r="D257" s="1">
-        <f t="shared" ref="D257:D320" si="4">IF(E257="","",COUNTIF(B:B,E257))</f>
+        <f t="shared" ref="D257:D288" si="4">IF(E257="","",COUNTIF(B:B,E257))</f>
         <v>1</v>
       </c>
       <c r="E257" s="1" t="s">
@@ -36132,4756 +36145,4768 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFE16AD0-5398-41FE-A4F8-EF22550BE4D0}">
-  <dimension ref="A1:E2016"/>
+  <dimension ref="A1:H289"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" style="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.7109375" style="26" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="26"/>
+    <col min="2" max="2" width="24.140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" style="26" customWidth="1"/>
+    <col min="4" max="4" width="33.28515625" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.7109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" style="26" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" style="26" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>994</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>996</v>
+        <v>1002</v>
       </c>
       <c r="D1" s="25" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E1" s="25" t="s">
         <v>997</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="F1" s="25" t="s">
         <v>998</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G1" s="25" t="s">
+        <v>1125</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
         <v>478</v>
       </c>
       <c r="B2" s="26" t="s">
+        <v>711</v>
+      </c>
+      <c r="D2" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="C2" s="26" t="s">
-        <v>711</v>
-      </c>
-      <c r="D2" s="26" t="s">
+      <c r="E2" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="F2" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
         <v>402</v>
       </c>
       <c r="B3" s="26" t="s">
+        <v>712</v>
+      </c>
+      <c r="D3" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="26" t="s">
-        <v>712</v>
-      </c>
-      <c r="D3" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="F3" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
         <v>117</v>
       </c>
       <c r="B4" s="26" t="s">
+        <v>713</v>
+      </c>
+      <c r="D4" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="C4" s="26" t="s">
-        <v>713</v>
-      </c>
-      <c r="D4" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="F4" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
         <v>164</v>
       </c>
       <c r="B5" s="26" t="s">
+        <v>714</v>
+      </c>
+      <c r="D5" s="26" t="s">
         <v>165</v>
       </c>
-      <c r="C5" s="26" t="s">
-        <v>714</v>
-      </c>
-      <c r="D5" s="26" t="s">
+      <c r="E5" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="F5" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
         <v>103</v>
       </c>
       <c r="B6" s="26" t="s">
+        <v>715</v>
+      </c>
+      <c r="D6" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="26" t="s">
-        <v>715</v>
-      </c>
-      <c r="D6" s="26" t="s">
+      <c r="E6" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="F6" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
         <v>471</v>
       </c>
       <c r="B7" s="26" t="s">
+        <v>716</v>
+      </c>
+      <c r="D7" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="26" t="s">
-        <v>716</v>
-      </c>
-      <c r="D7" s="26" t="s">
+      <c r="E7" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="F7" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
         <v>515</v>
       </c>
       <c r="B8" s="26" t="s">
+        <v>717</v>
+      </c>
+      <c r="D8" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="C8" s="26" t="s">
-        <v>717</v>
-      </c>
-      <c r="D8" s="26" t="s">
+      <c r="E8" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="F8" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
         <v>87</v>
       </c>
       <c r="B9" s="26" t="s">
+        <v>718</v>
+      </c>
+      <c r="D9" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="C9" s="26" t="s">
-        <v>718</v>
-      </c>
-      <c r="D9" s="26" t="s">
+      <c r="E9" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="F9" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
         <v>279</v>
       </c>
       <c r="B10" s="26" t="s">
+        <v>719</v>
+      </c>
+      <c r="D10" s="26" t="s">
         <v>280</v>
       </c>
-      <c r="C10" s="26" t="s">
-        <v>719</v>
-      </c>
-      <c r="D10" s="26" t="s">
+      <c r="E10" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="F10" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
         <v>475</v>
       </c>
       <c r="B11" s="26" t="s">
+        <v>720</v>
+      </c>
+      <c r="D11" s="26" t="s">
         <v>337</v>
       </c>
-      <c r="C11" s="26" t="s">
-        <v>720</v>
-      </c>
-      <c r="D11" s="26" t="s">
+      <c r="E11" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="F11" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B12" s="26" t="s">
+        <v>721</v>
+      </c>
+      <c r="D12" s="26" t="s">
         <v>346</v>
       </c>
-      <c r="C12" s="26" t="s">
-        <v>721</v>
-      </c>
-      <c r="D12" s="26" t="s">
+      <c r="E12" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="F12" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
         <v>272</v>
       </c>
       <c r="B13" s="26" t="s">
+        <v>722</v>
+      </c>
+      <c r="D13" s="26" t="s">
         <v>273</v>
       </c>
-      <c r="C13" s="26" t="s">
-        <v>722</v>
-      </c>
-      <c r="D13" s="26" t="s">
+      <c r="E13" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="F13" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B14" s="26" t="s">
+        <v>723</v>
+      </c>
+      <c r="D14" s="26" t="s">
         <v>143</v>
       </c>
-      <c r="C14" s="26" t="s">
-        <v>723</v>
-      </c>
-      <c r="D14" s="26" t="s">
+      <c r="E14" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="F14" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
         <v>599</v>
       </c>
       <c r="B15" s="26" t="s">
+        <v>724</v>
+      </c>
+      <c r="D15" s="26" t="s">
         <v>331</v>
       </c>
-      <c r="C15" s="26" t="s">
-        <v>724</v>
-      </c>
-      <c r="D15" s="26" t="s">
+      <c r="E15" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="F15" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="26" t="s">
         <v>502</v>
       </c>
       <c r="B16" s="26" t="s">
+        <v>725</v>
+      </c>
+      <c r="D16" s="26" t="s">
         <v>302</v>
       </c>
-      <c r="C16" s="26" t="s">
-        <v>725</v>
-      </c>
-      <c r="D16" s="26" t="s">
+      <c r="E16" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E16" s="26" t="s">
+      <c r="F16" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
         <v>79</v>
       </c>
       <c r="B17" s="26" t="s">
+        <v>726</v>
+      </c>
+      <c r="D17" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="26" t="s">
-        <v>726</v>
-      </c>
-      <c r="D17" s="26" t="s">
+      <c r="E17" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E17" s="26" t="s">
+      <c r="F17" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
         <v>502</v>
       </c>
       <c r="B18" s="26" t="s">
+        <v>727</v>
+      </c>
+      <c r="D18" s="26" t="s">
         <v>305</v>
       </c>
-      <c r="C18" s="26" t="s">
-        <v>727</v>
-      </c>
-      <c r="D18" s="26" t="s">
+      <c r="E18" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E18" s="26" t="s">
+      <c r="F18" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="26" t="s">
+        <v>728</v>
+      </c>
+      <c r="D19" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="C19" s="26" t="s">
-        <v>728</v>
-      </c>
-      <c r="D19" s="26" t="s">
+      <c r="E19" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E19" s="26" t="s">
+      <c r="F19" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
         <v>349</v>
       </c>
       <c r="B20" s="26" t="s">
+        <v>729</v>
+      </c>
+      <c r="D20" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="26" t="s">
-        <v>729</v>
-      </c>
-      <c r="D20" s="26" t="s">
+      <c r="E20" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="F20" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
         <v>503</v>
       </c>
       <c r="B21" s="26" t="s">
+        <v>730</v>
+      </c>
+      <c r="D21" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="26" t="s">
-        <v>730</v>
-      </c>
-      <c r="D21" s="26" t="s">
+      <c r="E21" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="F21" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
         <v>631</v>
       </c>
       <c r="B22" s="26" t="s">
+        <v>731</v>
+      </c>
+      <c r="D22" s="26" t="s">
         <v>363</v>
       </c>
-      <c r="C22" s="26" t="s">
-        <v>731</v>
-      </c>
-      <c r="D22" s="26" t="s">
+      <c r="E22" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="F22" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
         <v>239</v>
       </c>
       <c r="B23" s="26" t="s">
+        <v>732</v>
+      </c>
+      <c r="D23" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="C23" s="26" t="s">
-        <v>732</v>
-      </c>
-      <c r="D23" s="26" t="s">
+      <c r="E23" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="F23" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="26" t="s">
         <v>380</v>
       </c>
       <c r="B24" s="26" t="s">
+        <v>733</v>
+      </c>
+      <c r="D24" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="26" t="s">
-        <v>733</v>
-      </c>
-      <c r="D24" s="26" t="s">
+      <c r="E24" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="26" t="s">
+      <c r="F24" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
         <v>324</v>
       </c>
       <c r="B25" s="26" t="s">
+        <v>734</v>
+      </c>
+      <c r="D25" s="26" t="s">
         <v>265</v>
       </c>
-      <c r="C25" s="26" t="s">
-        <v>734</v>
-      </c>
-      <c r="D25" s="26" t="s">
+      <c r="E25" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E25" s="26" t="s">
+      <c r="F25" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B26" s="26" t="s">
+        <v>735</v>
+      </c>
+      <c r="D26" s="26" t="s">
         <v>407</v>
       </c>
-      <c r="C26" s="26" t="s">
-        <v>735</v>
-      </c>
-      <c r="D26" s="26" t="s">
+      <c r="E26" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E26" s="26" t="s">
+      <c r="F26" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
         <v>488</v>
       </c>
       <c r="B27" s="26" t="s">
+        <v>736</v>
+      </c>
+      <c r="D27" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="C27" s="26" t="s">
-        <v>736</v>
-      </c>
-      <c r="D27" s="26" t="s">
+      <c r="E27" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E27" s="26" t="s">
+      <c r="F27" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
         <v>27</v>
       </c>
       <c r="B28" s="26" t="s">
+        <v>737</v>
+      </c>
+      <c r="D28" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="26" t="s">
-        <v>737</v>
-      </c>
-      <c r="D28" s="26" t="s">
+      <c r="E28" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E28" s="26" t="s">
+      <c r="F28" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
         <v>504</v>
       </c>
       <c r="B29" s="26" t="s">
+        <v>738</v>
+      </c>
+      <c r="D29" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="C29" s="26" t="s">
-        <v>738</v>
-      </c>
-      <c r="D29" s="26" t="s">
+      <c r="E29" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E29" s="26" t="s">
+      <c r="F29" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="26" t="s">
         <v>340</v>
       </c>
       <c r="B30" s="26" t="s">
+        <v>739</v>
+      </c>
+      <c r="D30" s="26" t="s">
         <v>231</v>
       </c>
-      <c r="C30" s="26" t="s">
-        <v>739</v>
-      </c>
-      <c r="D30" s="26" t="s">
+      <c r="E30" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E30" s="26" t="s">
+      <c r="F30" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
         <v>306</v>
       </c>
       <c r="B31" s="26" t="s">
+        <v>740</v>
+      </c>
+      <c r="D31" s="26" t="s">
         <v>307</v>
       </c>
-      <c r="C31" s="26" t="s">
-        <v>740</v>
-      </c>
-      <c r="D31" s="26" t="s">
+      <c r="E31" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E31" s="26" t="s">
+      <c r="F31" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="26" t="s">
         <v>597</v>
       </c>
       <c r="B32" s="26" t="s">
+        <v>741</v>
+      </c>
+      <c r="D32" s="26" t="s">
         <v>227</v>
       </c>
-      <c r="C32" s="26" t="s">
-        <v>741</v>
-      </c>
-      <c r="D32" s="26" t="s">
+      <c r="E32" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E32" s="26" t="s">
+      <c r="F32" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
         <v>564</v>
       </c>
       <c r="B33" s="26" t="s">
+        <v>742</v>
+      </c>
+      <c r="D33" s="26" t="s">
         <v>274</v>
       </c>
-      <c r="C33" s="26" t="s">
-        <v>742</v>
-      </c>
-      <c r="D33" s="26" t="s">
+      <c r="E33" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E33" s="26" t="s">
+      <c r="F33" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="26" t="s">
         <v>12</v>
       </c>
       <c r="B34" s="26" t="s">
+        <v>743</v>
+      </c>
+      <c r="D34" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="26" t="s">
-        <v>743</v>
-      </c>
-      <c r="D34" s="26" t="s">
+      <c r="E34" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E34" s="26" t="s">
+      <c r="F34" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="26" t="s">
+        <v>744</v>
+      </c>
+      <c r="D35" s="26" t="s">
         <v>281</v>
       </c>
-      <c r="C35" s="26" t="s">
-        <v>744</v>
-      </c>
-      <c r="D35" s="26" t="s">
+      <c r="E35" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E35" s="26" t="s">
+      <c r="F35" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="26" t="s">
         <v>525</v>
       </c>
       <c r="B36" s="26" t="s">
+        <v>745</v>
+      </c>
+      <c r="D36" s="26" t="s">
         <v>405</v>
       </c>
-      <c r="C36" s="26" t="s">
-        <v>745</v>
-      </c>
-      <c r="D36" s="26" t="s">
+      <c r="E36" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E36" s="26" t="s">
+      <c r="F36" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="26" t="s">
         <v>526</v>
       </c>
       <c r="B37" s="26" t="s">
+        <v>746</v>
+      </c>
+      <c r="D37" s="26" t="s">
         <v>282</v>
       </c>
-      <c r="C37" s="26" t="s">
-        <v>746</v>
-      </c>
-      <c r="D37" s="26" t="s">
+      <c r="E37" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E37" s="26" t="s">
+      <c r="F37" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="26" t="s">
         <v>12</v>
       </c>
       <c r="B38" s="26" t="s">
+        <v>747</v>
+      </c>
+      <c r="D38" s="26" t="s">
         <v>420</v>
       </c>
-      <c r="C38" s="26" t="s">
-        <v>747</v>
-      </c>
-      <c r="D38" s="26" t="s">
+      <c r="E38" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E38" s="26" t="s">
+      <c r="F38" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
         <v>602</v>
       </c>
       <c r="B39" s="26" t="s">
+        <v>748</v>
+      </c>
+      <c r="D39" s="26" t="s">
         <v>229</v>
       </c>
-      <c r="C39" s="26" t="s">
-        <v>748</v>
-      </c>
-      <c r="D39" s="26" t="s">
+      <c r="E39" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E39" s="26" t="s">
+      <c r="F39" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B40" s="26" t="s">
+        <v>749</v>
+      </c>
+      <c r="D40" s="26" t="s">
         <v>283</v>
       </c>
-      <c r="C40" s="26" t="s">
-        <v>749</v>
-      </c>
-      <c r="D40" s="26" t="s">
+      <c r="E40" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E40" s="26" t="s">
+      <c r="F40" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
         <v>603</v>
       </c>
       <c r="B41" s="26" t="s">
+        <v>750</v>
+      </c>
+      <c r="D41" s="26" t="s">
         <v>328</v>
       </c>
-      <c r="C41" s="26" t="s">
-        <v>750</v>
-      </c>
-      <c r="D41" s="26" t="s">
+      <c r="E41" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E41" s="26" t="s">
+      <c r="F41" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="26" t="s">
         <v>95</v>
       </c>
       <c r="B42" s="26" t="s">
+        <v>751</v>
+      </c>
+      <c r="D42" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="C42" s="26" t="s">
-        <v>751</v>
-      </c>
-      <c r="D42" s="26" t="s">
+      <c r="E42" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E42" s="26" t="s">
+      <c r="F42" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
         <v>261</v>
       </c>
       <c r="B43" s="26" t="s">
+        <v>752</v>
+      </c>
+      <c r="D43" s="26" t="s">
         <v>262</v>
       </c>
-      <c r="C43" s="26" t="s">
-        <v>752</v>
-      </c>
-      <c r="D43" s="26" t="s">
+      <c r="E43" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E43" s="26" t="s">
+      <c r="F43" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="26" t="s">
         <v>216</v>
       </c>
       <c r="B44" s="26" t="s">
+        <v>753</v>
+      </c>
+      <c r="D44" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="C44" s="26" t="s">
-        <v>753</v>
-      </c>
-      <c r="D44" s="26" t="s">
+      <c r="E44" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E44" s="26" t="s">
+      <c r="F44" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B45" s="26" t="s">
+        <v>754</v>
+      </c>
+      <c r="D45" s="26" t="s">
         <v>421</v>
       </c>
-      <c r="C45" s="26" t="s">
-        <v>754</v>
-      </c>
-      <c r="D45" s="26" t="s">
+      <c r="E45" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E45" s="26" t="s">
+      <c r="F45" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B46" s="26" t="s">
+        <v>755</v>
+      </c>
+      <c r="D46" s="26" t="s">
         <v>426</v>
       </c>
-      <c r="C46" s="26" t="s">
-        <v>755</v>
-      </c>
-      <c r="D46" s="26" t="s">
+      <c r="E46" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E46" s="26" t="s">
+      <c r="F46" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B47" s="26" t="s">
+        <v>756</v>
+      </c>
+      <c r="D47" s="26" t="s">
         <v>364</v>
       </c>
-      <c r="C47" s="26" t="s">
-        <v>756</v>
-      </c>
-      <c r="D47" s="26" t="s">
+      <c r="E47" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E47" s="26" t="s">
+      <c r="F47" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="26" t="s">
         <v>213</v>
       </c>
       <c r="B48" s="26" t="s">
+        <v>757</v>
+      </c>
+      <c r="D48" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="C48" s="26" t="s">
-        <v>757</v>
-      </c>
-      <c r="D48" s="26" t="s">
+      <c r="E48" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E48" s="26" t="s">
+      <c r="F48" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
         <v>568</v>
       </c>
       <c r="B49" s="26" t="s">
+        <v>758</v>
+      </c>
+      <c r="D49" s="26" t="s">
         <v>381</v>
       </c>
-      <c r="C49" s="26" t="s">
-        <v>758</v>
-      </c>
-      <c r="D49" s="26" t="s">
+      <c r="E49" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E49" s="26" t="s">
+      <c r="F49" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="26" t="s">
         <v>142</v>
       </c>
       <c r="B50" s="26" t="s">
+        <v>759</v>
+      </c>
+      <c r="D50" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="C50" s="26" t="s">
-        <v>759</v>
-      </c>
-      <c r="D50" s="26" t="s">
+      <c r="E50" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E50" s="26" t="s">
+      <c r="F50" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="26" t="s">
         <v>465</v>
       </c>
       <c r="B51" s="26" t="s">
+        <v>760</v>
+      </c>
+      <c r="D51" s="26" t="s">
         <v>353</v>
       </c>
-      <c r="C51" s="26" t="s">
-        <v>760</v>
-      </c>
-      <c r="D51" s="26" t="s">
+      <c r="E51" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E51" s="26" t="s">
+      <c r="F51" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="26" t="s">
         <v>154</v>
       </c>
       <c r="B52" s="26" t="s">
+        <v>761</v>
+      </c>
+      <c r="D52" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="26" t="s">
-        <v>761</v>
-      </c>
-      <c r="D52" s="26" t="s">
+      <c r="E52" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E52" s="26" t="s">
+      <c r="F52" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="26" t="s">
         <v>191</v>
       </c>
       <c r="B53" s="26" t="s">
+        <v>762</v>
+      </c>
+      <c r="D53" s="26" t="s">
         <v>192</v>
       </c>
-      <c r="C53" s="26" t="s">
-        <v>762</v>
-      </c>
-      <c r="D53" s="26" t="s">
+      <c r="E53" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E53" s="26" t="s">
+      <c r="F53" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="26" t="s">
         <v>233</v>
       </c>
       <c r="B54" s="26" t="s">
+        <v>763</v>
+      </c>
+      <c r="D54" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="C54" s="26" t="s">
-        <v>763</v>
-      </c>
-      <c r="D54" s="26" t="s">
+      <c r="E54" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E54" s="26" t="s">
+      <c r="F54" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
         <v>208</v>
       </c>
       <c r="B55" s="26" t="s">
+        <v>764</v>
+      </c>
+      <c r="D55" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="C55" s="26" t="s">
-        <v>764</v>
-      </c>
-      <c r="D55" s="26" t="s">
+      <c r="E55" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E55" s="26" t="s">
+      <c r="F55" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="26" t="s">
         <v>514</v>
       </c>
       <c r="B56" s="26" t="s">
+        <v>765</v>
+      </c>
+      <c r="D56" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C56" s="26" t="s">
-        <v>765</v>
-      </c>
-      <c r="D56" s="26" t="s">
+      <c r="E56" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E56" s="26" t="s">
+      <c r="F56" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
         <v>581</v>
       </c>
       <c r="B57" s="26" t="s">
+        <v>766</v>
+      </c>
+      <c r="D57" s="26" t="s">
         <v>425</v>
       </c>
-      <c r="C57" s="26" t="s">
-        <v>766</v>
-      </c>
-      <c r="D57" s="26" t="s">
+      <c r="E57" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E57" s="26" t="s">
+      <c r="F57" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="26" t="s">
         <v>638</v>
       </c>
       <c r="B58" s="26" t="s">
+        <v>767</v>
+      </c>
+      <c r="D58" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="C58" s="26" t="s">
-        <v>767</v>
-      </c>
-      <c r="D58" s="26" t="s">
+      <c r="E58" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E58" s="26" t="s">
+      <c r="F58" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
         <v>516</v>
       </c>
       <c r="B59" s="26" t="s">
+        <v>768</v>
+      </c>
+      <c r="D59" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="C59" s="26" t="s">
-        <v>768</v>
-      </c>
-      <c r="D59" s="26" t="s">
+      <c r="E59" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E59" s="26" t="s">
+      <c r="F59" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="26" t="s">
         <v>573</v>
       </c>
       <c r="B60" s="26" t="s">
+        <v>769</v>
+      </c>
+      <c r="D60" s="26" t="s">
         <v>378</v>
       </c>
-      <c r="C60" s="26" t="s">
-        <v>769</v>
-      </c>
-      <c r="D60" s="26" t="s">
+      <c r="E60" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E60" s="26" t="s">
+      <c r="F60" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
         <v>399</v>
       </c>
       <c r="B61" s="26" t="s">
+        <v>770</v>
+      </c>
+      <c r="D61" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C61" s="26" t="s">
-        <v>770</v>
-      </c>
-      <c r="D61" s="26" t="s">
+      <c r="E61" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E61" s="26" t="s">
+      <c r="F61" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="26" t="s">
         <v>243</v>
       </c>
       <c r="B62" s="26" t="s">
+        <v>771</v>
+      </c>
+      <c r="D62" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="C62" s="26" t="s">
-        <v>771</v>
-      </c>
-      <c r="D62" s="26" t="s">
+      <c r="E62" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E62" s="26" t="s">
+      <c r="F62" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="26" t="s">
         <v>481</v>
       </c>
       <c r="B63" s="26" t="s">
+        <v>772</v>
+      </c>
+      <c r="D63" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="C63" s="26" t="s">
-        <v>772</v>
-      </c>
-      <c r="D63" s="26" t="s">
+      <c r="E63" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E63" s="26" t="s">
+      <c r="F63" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="26" t="s">
         <v>506</v>
       </c>
       <c r="B64" s="26" t="s">
+        <v>773</v>
+      </c>
+      <c r="D64" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="C64" s="26" t="s">
-        <v>773</v>
-      </c>
-      <c r="D64" s="26" t="s">
+      <c r="E64" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E64" s="26" t="s">
+      <c r="F64" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="26" t="s">
         <v>269</v>
       </c>
       <c r="B65" s="26" t="s">
+        <v>774</v>
+      </c>
+      <c r="D65" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="C65" s="26" t="s">
-        <v>774</v>
-      </c>
-      <c r="D65" s="26" t="s">
+      <c r="E65" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E65" s="26" t="s">
+      <c r="F65" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="26" t="s">
         <v>468</v>
       </c>
       <c r="B66" s="26" t="s">
+        <v>775</v>
+      </c>
+      <c r="D66" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="C66" s="26" t="s">
-        <v>775</v>
-      </c>
-      <c r="D66" s="26" t="s">
+      <c r="E66" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E66" s="26" t="s">
+      <c r="F66" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="26" t="s">
         <v>559</v>
       </c>
       <c r="B67" s="26" t="s">
+        <v>776</v>
+      </c>
+      <c r="D67" s="26" t="s">
         <v>312</v>
       </c>
-      <c r="C67" s="26" t="s">
-        <v>776</v>
-      </c>
-      <c r="D67" s="26" t="s">
+      <c r="E67" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E67" s="26" t="s">
+      <c r="F67" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="26" t="s">
         <v>485</v>
       </c>
       <c r="B68" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="D68" s="26" t="s">
         <v>391</v>
       </c>
-      <c r="C68" s="26" t="s">
-        <v>777</v>
-      </c>
-      <c r="D68" s="26" t="s">
+      <c r="E68" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E68" s="26" t="s">
+      <c r="F68" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="26" t="s">
         <v>607</v>
       </c>
       <c r="B69" s="26" t="s">
+        <v>778</v>
+      </c>
+      <c r="D69" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="C69" s="26" t="s">
-        <v>778</v>
-      </c>
-      <c r="D69" s="26" t="s">
+      <c r="E69" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E69" s="26" t="s">
+      <c r="F69" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="26" t="s">
         <v>451</v>
       </c>
       <c r="B70" s="26" t="s">
+        <v>779</v>
+      </c>
+      <c r="D70" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="C70" s="26" t="s">
-        <v>779</v>
-      </c>
-      <c r="D70" s="26" t="s">
+      <c r="E70" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E70" s="26" t="s">
+      <c r="F70" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="26" t="s">
         <v>706</v>
       </c>
       <c r="B71" s="26" t="s">
+        <v>780</v>
+      </c>
+      <c r="D71" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="C71" s="26" t="s">
-        <v>780</v>
-      </c>
-      <c r="D71" s="26" t="s">
+      <c r="E71" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E71" s="26" t="s">
+      <c r="F71" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="26" t="s">
         <v>362</v>
       </c>
       <c r="B72" s="26" t="s">
+        <v>781</v>
+      </c>
+      <c r="D72" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="C72" s="26" t="s">
-        <v>781</v>
-      </c>
-      <c r="D72" s="26" t="s">
+      <c r="E72" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E72" s="26" t="s">
+      <c r="F72" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B73" s="26" t="s">
+        <v>782</v>
+      </c>
+      <c r="D73" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="C73" s="26" t="s">
-        <v>782</v>
-      </c>
-      <c r="D73" s="26" t="s">
+      <c r="E73" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E73" s="26" t="s">
+      <c r="F73" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="26" t="s">
         <v>578</v>
       </c>
       <c r="B74" s="26" t="s">
+        <v>783</v>
+      </c>
+      <c r="D74" s="26" t="s">
         <v>325</v>
       </c>
-      <c r="C74" s="26" t="s">
-        <v>783</v>
-      </c>
-      <c r="D74" s="26" t="s">
+      <c r="E74" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E74" s="26" t="s">
+      <c r="F74" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="26" t="s">
         <v>470</v>
       </c>
       <c r="B75" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="D75" s="26" t="s">
         <v>319</v>
       </c>
-      <c r="C75" s="26" t="s">
-        <v>784</v>
-      </c>
-      <c r="D75" s="26" t="s">
+      <c r="E75" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E75" s="26" t="s">
+      <c r="F75" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="26" t="s">
         <v>284</v>
       </c>
       <c r="B76" s="26" t="s">
+        <v>785</v>
+      </c>
+      <c r="D76" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="C76" s="26" t="s">
-        <v>785</v>
-      </c>
-      <c r="D76" s="26" t="s">
+      <c r="E76" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E76" s="26" t="s">
+      <c r="F76" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="26" t="s">
         <v>607</v>
       </c>
       <c r="B77" s="26" t="s">
+        <v>786</v>
+      </c>
+      <c r="D77" s="26" t="s">
         <v>365</v>
       </c>
-      <c r="C77" s="26" t="s">
-        <v>786</v>
-      </c>
-      <c r="D77" s="26" t="s">
+      <c r="E77" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E77" s="26" t="s">
+      <c r="F77" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="26" t="s">
         <v>440</v>
       </c>
       <c r="B78" s="26" t="s">
+        <v>787</v>
+      </c>
+      <c r="D78" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="C78" s="26" t="s">
-        <v>787</v>
-      </c>
-      <c r="D78" s="26" t="s">
+      <c r="E78" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E78" s="26" t="s">
+      <c r="F78" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="26" t="s">
         <v>513</v>
       </c>
       <c r="B79" s="26" t="s">
+        <v>788</v>
+      </c>
+      <c r="D79" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="C79" s="26" t="s">
-        <v>788</v>
-      </c>
-      <c r="D79" s="26" t="s">
+      <c r="E79" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E79" s="26" t="s">
+      <c r="F79" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="26" t="s">
         <v>400</v>
       </c>
       <c r="B80" s="26" t="s">
+        <v>789</v>
+      </c>
+      <c r="D80" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="C80" s="26" t="s">
-        <v>789</v>
-      </c>
-      <c r="D80" s="26" t="s">
+      <c r="E80" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E80" s="26" t="s">
+      <c r="F80" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="26" t="s">
         <v>608</v>
       </c>
       <c r="B81" s="26" t="s">
+        <v>790</v>
+      </c>
+      <c r="D81" s="26" t="s">
         <v>258</v>
       </c>
-      <c r="C81" s="26" t="s">
-        <v>790</v>
-      </c>
-      <c r="D81" s="26" t="s">
+      <c r="E81" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E81" s="26" t="s">
+      <c r="F81" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="26" t="s">
         <v>438</v>
       </c>
       <c r="B82" s="26" t="s">
+        <v>791</v>
+      </c>
+      <c r="D82" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="C82" s="26" t="s">
-        <v>791</v>
-      </c>
-      <c r="D82" s="26" t="s">
+      <c r="E82" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E82" s="26" t="s">
+      <c r="F82" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="26" t="s">
         <v>351</v>
       </c>
       <c r="B83" s="26" t="s">
+        <v>792</v>
+      </c>
+      <c r="D83" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C83" s="26" t="s">
-        <v>792</v>
-      </c>
-      <c r="D83" s="26" t="s">
+      <c r="E83" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E83" s="26" t="s">
+      <c r="F83" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="26" t="s">
         <v>160</v>
       </c>
       <c r="B84" s="26" t="s">
+        <v>793</v>
+      </c>
+      <c r="D84" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="C84" s="26" t="s">
-        <v>793</v>
-      </c>
-      <c r="D84" s="26" t="s">
+      <c r="E84" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E84" s="26" t="s">
+      <c r="F84" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="26" t="s">
         <v>571</v>
       </c>
       <c r="B85" s="26" t="s">
+        <v>794</v>
+      </c>
+      <c r="D85" s="26" t="s">
         <v>382</v>
       </c>
-      <c r="C85" s="26" t="s">
-        <v>794</v>
-      </c>
-      <c r="D85" s="26" t="s">
+      <c r="E85" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E85" s="26" t="s">
+      <c r="F85" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B86" s="26" t="s">
+        <v>795</v>
+      </c>
+      <c r="D86" s="26" t="s">
         <v>406</v>
       </c>
-      <c r="C86" s="26" t="s">
-        <v>795</v>
-      </c>
-      <c r="D86" s="26" t="s">
+      <c r="E86" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E86" s="26" t="s">
+      <c r="F86" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="26" t="s">
         <v>120</v>
       </c>
       <c r="B87" s="26" t="s">
+        <v>796</v>
+      </c>
+      <c r="D87" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="C87" s="26" t="s">
-        <v>796</v>
-      </c>
-      <c r="D87" s="26" t="s">
+      <c r="E87" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E87" s="26" t="s">
+      <c r="F87" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="26" t="s">
         <v>44</v>
       </c>
       <c r="B88" s="26" t="s">
+        <v>797</v>
+      </c>
+      <c r="D88" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="C88" s="26" t="s">
-        <v>797</v>
-      </c>
-      <c r="D88" s="26" t="s">
+      <c r="E88" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E88" s="26" t="s">
+      <c r="F88" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="26" t="s">
         <v>219</v>
       </c>
       <c r="B89" s="26" t="s">
+        <v>798</v>
+      </c>
+      <c r="D89" s="26" t="s">
         <v>220</v>
       </c>
-      <c r="C89" s="26" t="s">
-        <v>798</v>
-      </c>
-      <c r="D89" s="26" t="s">
+      <c r="E89" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E89" s="26" t="s">
+      <c r="F89" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="26" t="s">
         <v>432</v>
       </c>
       <c r="B90" s="26" t="s">
+        <v>799</v>
+      </c>
+      <c r="D90" s="26" t="s">
         <v>275</v>
       </c>
-      <c r="C90" s="26" t="s">
-        <v>799</v>
-      </c>
-      <c r="D90" s="26" t="s">
+      <c r="E90" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E90" s="26" t="s">
+      <c r="F90" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="26" t="s">
         <v>19</v>
       </c>
       <c r="B91" s="26" t="s">
+        <v>800</v>
+      </c>
+      <c r="D91" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="C91" s="26" t="s">
-        <v>800</v>
-      </c>
-      <c r="D91" s="26" t="s">
+      <c r="E91" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E91" s="26" t="s">
+      <c r="F91" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B92" s="26" t="s">
+        <v>801</v>
+      </c>
+      <c r="D92" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="C92" s="26" t="s">
-        <v>801</v>
-      </c>
-      <c r="D92" s="26" t="s">
+      <c r="E92" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E92" s="26" t="s">
+      <c r="F92" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="26" t="s">
         <v>419</v>
       </c>
       <c r="B93" s="26" t="s">
+        <v>802</v>
+      </c>
+      <c r="D93" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="C93" s="26" t="s">
-        <v>802</v>
-      </c>
-      <c r="D93" s="26" t="s">
+      <c r="E93" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E93" s="26" t="s">
+      <c r="F93" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="26" t="s">
         <v>640</v>
       </c>
       <c r="B94" s="26" t="s">
+        <v>803</v>
+      </c>
+      <c r="D94" s="26" t="s">
         <v>372</v>
       </c>
-      <c r="C94" s="26" t="s">
-        <v>803</v>
-      </c>
-      <c r="D94" s="26" t="s">
+      <c r="E94" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E94" s="26" t="s">
+      <c r="F94" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="26" t="s">
         <v>453</v>
       </c>
       <c r="B95" s="26" t="s">
+        <v>804</v>
+      </c>
+      <c r="D95" s="26" t="s">
         <v>252</v>
       </c>
-      <c r="C95" s="26" t="s">
-        <v>804</v>
-      </c>
-      <c r="D95" s="26" t="s">
+      <c r="E95" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E95" s="26" t="s">
+      <c r="F95" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="26" t="s">
         <v>628</v>
       </c>
       <c r="B96" s="26" t="s">
+        <v>805</v>
+      </c>
+      <c r="D96" s="26" t="s">
         <v>427</v>
       </c>
-      <c r="C96" s="26" t="s">
-        <v>805</v>
-      </c>
-      <c r="D96" s="26" t="s">
+      <c r="E96" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E96" s="26" t="s">
+      <c r="F96" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="26" t="s">
         <v>221</v>
       </c>
       <c r="B97" s="26" t="s">
+        <v>806</v>
+      </c>
+      <c r="D97" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C97" s="26" t="s">
-        <v>806</v>
-      </c>
-      <c r="D97" s="26" t="s">
+      <c r="E97" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E97" s="26" t="s">
+      <c r="F97" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="26" t="s">
         <v>112</v>
       </c>
       <c r="B98" s="26" t="s">
+        <v>807</v>
+      </c>
+      <c r="D98" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="C98" s="26" t="s">
-        <v>807</v>
-      </c>
-      <c r="D98" s="26" t="s">
+      <c r="E98" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E98" s="26" t="s">
+      <c r="F98" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="26" t="s">
         <v>531</v>
       </c>
       <c r="B99" s="26" t="s">
+        <v>808</v>
+      </c>
+      <c r="D99" s="26" t="s">
         <v>422</v>
       </c>
-      <c r="C99" s="26" t="s">
-        <v>808</v>
-      </c>
-      <c r="D99" s="26" t="s">
+      <c r="E99" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E99" s="26" t="s">
+      <c r="F99" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="26" t="s">
         <v>641</v>
       </c>
       <c r="B100" s="26" t="s">
+        <v>809</v>
+      </c>
+      <c r="D100" s="26" t="s">
         <v>308</v>
       </c>
-      <c r="C100" s="26" t="s">
-        <v>809</v>
-      </c>
-      <c r="D100" s="26" t="s">
+      <c r="E100" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E100" s="26" t="s">
+      <c r="F100" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="26" t="s">
         <v>572</v>
       </c>
       <c r="B101" s="26" t="s">
+        <v>810</v>
+      </c>
+      <c r="D101" s="26" t="s">
         <v>314</v>
       </c>
-      <c r="C101" s="26" t="s">
-        <v>810</v>
-      </c>
-      <c r="D101" s="26" t="s">
+      <c r="E101" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E101" s="26" t="s">
+      <c r="F101" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="26" t="s">
         <v>228</v>
       </c>
       <c r="B102" s="26" t="s">
+        <v>811</v>
+      </c>
+      <c r="D102" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="C102" s="26" t="s">
-        <v>811</v>
-      </c>
-      <c r="D102" s="26" t="s">
+      <c r="E102" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E102" s="26" t="s">
+      <c r="F102" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="26" t="s">
         <v>189</v>
       </c>
       <c r="B103" s="26" t="s">
+        <v>812</v>
+      </c>
+      <c r="D103" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="C103" s="26" t="s">
-        <v>812</v>
-      </c>
-      <c r="D103" s="26" t="s">
+      <c r="E103" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E103" s="26" t="s">
+      <c r="F103" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="26" t="s">
         <v>245</v>
       </c>
       <c r="B104" s="26" t="s">
+        <v>813</v>
+      </c>
+      <c r="D104" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="C104" s="26" t="s">
-        <v>813</v>
-      </c>
-      <c r="D104" s="26" t="s">
+      <c r="E104" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E104" s="26" t="s">
+      <c r="F104" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="26" t="s">
         <v>19</v>
       </c>
       <c r="B105" s="26" t="s">
+        <v>814</v>
+      </c>
+      <c r="D105" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="C105" s="26" t="s">
-        <v>814</v>
-      </c>
-      <c r="D105" s="26" t="s">
+      <c r="E105" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E105" s="26" t="s">
+      <c r="F105" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="26" t="s">
         <v>474</v>
       </c>
       <c r="B106" s="26" t="s">
+        <v>815</v>
+      </c>
+      <c r="D106" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="C106" s="26" t="s">
-        <v>815</v>
-      </c>
-      <c r="D106" s="26" t="s">
+      <c r="E106" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E106" s="26" t="s">
+      <c r="F106" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="26" t="s">
         <v>316</v>
       </c>
       <c r="B107" s="26" t="s">
+        <v>816</v>
+      </c>
+      <c r="D107" s="26" t="s">
         <v>317</v>
       </c>
-      <c r="C107" s="26" t="s">
-        <v>816</v>
-      </c>
-      <c r="D107" s="26" t="s">
+      <c r="E107" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E107" s="26" t="s">
+      <c r="F107" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="26" t="s">
         <v>195</v>
       </c>
       <c r="B108" s="26" t="s">
+        <v>817</v>
+      </c>
+      <c r="D108" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="C108" s="26" t="s">
-        <v>817</v>
-      </c>
-      <c r="D108" s="26" t="s">
+      <c r="E108" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E108" s="26" t="s">
+      <c r="F108" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="26" t="s">
         <v>507</v>
       </c>
       <c r="B109" s="26" t="s">
+        <v>818</v>
+      </c>
+      <c r="D109" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="C109" s="26" t="s">
-        <v>818</v>
-      </c>
-      <c r="D109" s="26" t="s">
+      <c r="E109" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E109" s="26" t="s">
+      <c r="F109" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B110" s="26" t="s">
+        <v>819</v>
+      </c>
+      <c r="D110" s="26" t="s">
         <v>336</v>
       </c>
-      <c r="C110" s="26" t="s">
-        <v>819</v>
-      </c>
-      <c r="D110" s="26" t="s">
+      <c r="E110" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E110" s="26" t="s">
+      <c r="F110" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B111" s="26" t="s">
+        <v>820</v>
+      </c>
+      <c r="D111" s="26" t="s">
         <v>392</v>
       </c>
-      <c r="C111" s="26" t="s">
-        <v>820</v>
-      </c>
-      <c r="D111" s="26" t="s">
+      <c r="E111" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E111" s="26" t="s">
+      <c r="F111" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="26" t="s">
         <v>235</v>
       </c>
       <c r="B112" s="26" t="s">
+        <v>821</v>
+      </c>
+      <c r="D112" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="C112" s="26" t="s">
-        <v>821</v>
-      </c>
-      <c r="D112" s="26" t="s">
+      <c r="E112" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E112" s="26" t="s">
+      <c r="F112" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B113" s="26" t="s">
+        <v>822</v>
+      </c>
+      <c r="D113" s="26" t="s">
         <v>373</v>
       </c>
-      <c r="C113" s="26" t="s">
-        <v>822</v>
-      </c>
-      <c r="D113" s="26" t="s">
+      <c r="E113" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E113" s="26" t="s">
+      <c r="F113" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B114" s="26" t="s">
+        <v>823</v>
+      </c>
+      <c r="D114" s="26" t="s">
         <v>414</v>
       </c>
-      <c r="C114" s="26" t="s">
-        <v>823</v>
-      </c>
-      <c r="D114" s="26" t="s">
+      <c r="E114" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E114" s="26" t="s">
+      <c r="F114" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="26" t="s">
         <v>8</v>
       </c>
       <c r="B115" s="26" t="s">
+        <v>824</v>
+      </c>
+      <c r="D115" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C115" s="26" t="s">
-        <v>824</v>
-      </c>
-      <c r="D115" s="26" t="s">
+      <c r="E115" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E115" s="26" t="s">
+      <c r="F115" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="26" t="s">
         <v>643</v>
       </c>
       <c r="B116" s="26" t="s">
+        <v>825</v>
+      </c>
+      <c r="D116" s="26" t="s">
         <v>415</v>
       </c>
-      <c r="C116" s="26" t="s">
-        <v>825</v>
-      </c>
-      <c r="D116" s="26" t="s">
+      <c r="E116" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E116" s="26" t="s">
+      <c r="F116" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B117" s="26" t="s">
+        <v>826</v>
+      </c>
+      <c r="D117" s="26" t="s">
         <v>413</v>
       </c>
-      <c r="C117" s="26" t="s">
-        <v>826</v>
-      </c>
-      <c r="D117" s="26" t="s">
+      <c r="E117" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E117" s="26" t="s">
+      <c r="F117" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B118" s="26" t="s">
+        <v>827</v>
+      </c>
+      <c r="D118" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="C118" s="26" t="s">
-        <v>827</v>
-      </c>
-      <c r="D118" s="26" t="s">
+      <c r="E118" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E118" s="26" t="s">
+      <c r="F118" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="26" t="s">
         <v>277</v>
       </c>
       <c r="B119" s="26" t="s">
+        <v>828</v>
+      </c>
+      <c r="D119" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="C119" s="26" t="s">
-        <v>828</v>
-      </c>
-      <c r="D119" s="26" t="s">
+      <c r="E119" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E119" s="26" t="s">
+      <c r="F119" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="26" t="s">
         <v>708</v>
       </c>
       <c r="B120" s="26" t="s">
+        <v>829</v>
+      </c>
+      <c r="D120" s="26" t="s">
         <v>347</v>
       </c>
-      <c r="C120" s="26" t="s">
-        <v>829</v>
-      </c>
-      <c r="D120" s="26" t="s">
+      <c r="E120" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E120" s="26" t="s">
+      <c r="F120" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="26" t="s">
         <v>707</v>
       </c>
       <c r="B121" s="26" t="s">
+        <v>830</v>
+      </c>
+      <c r="D121" s="26" t="s">
         <v>348</v>
       </c>
-      <c r="C121" s="26" t="s">
-        <v>830</v>
-      </c>
-      <c r="D121" s="26" t="s">
+      <c r="E121" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E121" s="26" t="s">
+      <c r="F121" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="26" t="s">
         <v>125</v>
       </c>
       <c r="B122" s="26" t="s">
+        <v>831</v>
+      </c>
+      <c r="D122" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="C122" s="26" t="s">
-        <v>831</v>
-      </c>
-      <c r="D122" s="26" t="s">
+      <c r="E122" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E122" s="26" t="s">
+      <c r="F122" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="26" t="s">
         <v>578</v>
       </c>
       <c r="B123" s="26" t="s">
+        <v>832</v>
+      </c>
+      <c r="D123" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C123" s="26" t="s">
-        <v>832</v>
-      </c>
-      <c r="D123" s="26" t="s">
+      <c r="E123" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E123" s="26" t="s">
+      <c r="F123" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="26" t="s">
         <v>443</v>
       </c>
       <c r="B124" s="26" t="s">
+        <v>833</v>
+      </c>
+      <c r="D124" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="C124" s="26" t="s">
-        <v>833</v>
-      </c>
-      <c r="D124" s="26" t="s">
+      <c r="E124" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E124" s="26" t="s">
+      <c r="F124" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="26" t="s">
         <v>390</v>
       </c>
       <c r="B125" s="26" t="s">
+        <v>834</v>
+      </c>
+      <c r="D125" s="26" t="s">
         <v>366</v>
       </c>
-      <c r="C125" s="26" t="s">
-        <v>834</v>
-      </c>
-      <c r="D125" s="26" t="s">
+      <c r="E125" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E125" s="26" t="s">
+      <c r="F125" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="26" t="s">
         <v>476</v>
       </c>
       <c r="B126" s="26" t="s">
+        <v>835</v>
+      </c>
+      <c r="D126" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="C126" s="26" t="s">
-        <v>835</v>
-      </c>
-      <c r="D126" s="26" t="s">
+      <c r="E126" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E126" s="26" t="s">
+      <c r="F126" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="26" t="s">
         <v>443</v>
       </c>
       <c r="B127" s="26" t="s">
+        <v>836</v>
+      </c>
+      <c r="D127" s="26" t="s">
         <v>393</v>
       </c>
-      <c r="C127" s="26" t="s">
-        <v>836</v>
-      </c>
-      <c r="D127" s="26" t="s">
+      <c r="E127" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E127" s="26" t="s">
+      <c r="F127" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="26" t="s">
         <v>578</v>
       </c>
       <c r="B128" s="26" t="s">
+        <v>837</v>
+      </c>
+      <c r="D128" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="C128" s="26" t="s">
-        <v>837</v>
-      </c>
-      <c r="D128" s="26" t="s">
+      <c r="E128" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E128" s="26" t="s">
+      <c r="F128" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="26" t="s">
         <v>578</v>
       </c>
       <c r="B129" s="26" t="s">
+        <v>838</v>
+      </c>
+      <c r="D129" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="C129" s="26" t="s">
-        <v>838</v>
-      </c>
-      <c r="D129" s="26" t="s">
+      <c r="E129" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E129" s="26" t="s">
+      <c r="F129" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="26" t="s">
         <v>433</v>
       </c>
       <c r="B130" s="26" t="s">
+        <v>839</v>
+      </c>
+      <c r="D130" s="26" t="s">
         <v>194</v>
       </c>
-      <c r="C130" s="26" t="s">
-        <v>839</v>
-      </c>
-      <c r="D130" s="26" t="s">
+      <c r="E130" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E130" s="26" t="s">
+      <c r="F130" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="26" t="s">
         <v>158</v>
       </c>
       <c r="B131" s="26" t="s">
+        <v>840</v>
+      </c>
+      <c r="D131" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C131" s="26" t="s">
-        <v>840</v>
-      </c>
-      <c r="D131" s="26" t="s">
+      <c r="E131" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E131" s="26" t="s">
+      <c r="F131" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="26" t="s">
         <v>109</v>
       </c>
       <c r="B132" s="26" t="s">
+        <v>841</v>
+      </c>
+      <c r="D132" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="C132" s="26" t="s">
-        <v>841</v>
-      </c>
-      <c r="D132" s="26" t="s">
+      <c r="E132" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E132" s="26" t="s">
+      <c r="F132" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="26" t="s">
         <v>335</v>
       </c>
       <c r="B133" s="26" t="s">
+        <v>842</v>
+      </c>
+      <c r="D133" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="C133" s="26" t="s">
-        <v>842</v>
-      </c>
-      <c r="D133" s="26" t="s">
+      <c r="E133" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E133" s="26" t="s">
+      <c r="F133" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="26" t="s">
         <v>40</v>
       </c>
       <c r="B134" s="26" t="s">
+        <v>843</v>
+      </c>
+      <c r="D134" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="C134" s="26" t="s">
-        <v>843</v>
-      </c>
-      <c r="D134" s="26" t="s">
+      <c r="E134" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E134" s="26" t="s">
+      <c r="F134" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="26" t="s">
         <v>651</v>
       </c>
       <c r="B135" s="26" t="s">
+        <v>844</v>
+      </c>
+      <c r="D135" s="26" t="s">
         <v>394</v>
       </c>
-      <c r="C135" s="26" t="s">
-        <v>844</v>
-      </c>
-      <c r="D135" s="26" t="s">
+      <c r="E135" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E135" s="26" t="s">
+      <c r="F135" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="26" t="s">
         <v>187</v>
       </c>
       <c r="B136" s="26" t="s">
+        <v>845</v>
+      </c>
+      <c r="D136" s="26" t="s">
         <v>188</v>
       </c>
-      <c r="C136" s="26" t="s">
-        <v>845</v>
-      </c>
-      <c r="D136" s="26" t="s">
+      <c r="E136" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E136" s="26" t="s">
+      <c r="F136" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="26" t="s">
         <v>444</v>
       </c>
       <c r="B137" s="26" t="s">
+        <v>846</v>
+      </c>
+      <c r="D137" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="C137" s="26" t="s">
-        <v>846</v>
-      </c>
-      <c r="D137" s="26" t="s">
+      <c r="E137" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E137" s="26" t="s">
+      <c r="F137" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="26" t="s">
         <v>654</v>
       </c>
       <c r="B138" s="26" t="s">
+        <v>847</v>
+      </c>
+      <c r="D138" s="26" t="s">
         <v>395</v>
       </c>
-      <c r="C138" s="26" t="s">
-        <v>847</v>
-      </c>
-      <c r="D138" s="26" t="s">
+      <c r="E138" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E138" s="26" t="s">
+      <c r="F138" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="26" t="s">
         <v>134</v>
       </c>
       <c r="B139" s="26" t="s">
+        <v>848</v>
+      </c>
+      <c r="D139" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="C139" s="26" t="s">
-        <v>848</v>
-      </c>
-      <c r="D139" s="26" t="s">
+      <c r="E139" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E139" s="26" t="s">
+      <c r="F139" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="26" t="s">
         <v>23</v>
       </c>
       <c r="B140" s="26" t="s">
+        <v>849</v>
+      </c>
+      <c r="D140" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C140" s="26" t="s">
-        <v>849</v>
-      </c>
-      <c r="D140" s="26" t="s">
+      <c r="E140" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E140" s="26" t="s">
+      <c r="F140" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="26" t="s">
         <v>578</v>
       </c>
       <c r="B141" s="26" t="s">
+        <v>850</v>
+      </c>
+      <c r="D141" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="C141" s="26" t="s">
-        <v>850</v>
-      </c>
-      <c r="D141" s="26" t="s">
+      <c r="E141" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E141" s="26" t="s">
+      <c r="F141" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="26" t="s">
         <v>578</v>
       </c>
       <c r="B142" s="26" t="s">
+        <v>851</v>
+      </c>
+      <c r="D142" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="C142" s="26" t="s">
-        <v>851</v>
-      </c>
-      <c r="D142" s="26" t="s">
+      <c r="E142" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E142" s="26" t="s">
+      <c r="F142" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="26" t="s">
         <v>304</v>
       </c>
       <c r="B143" s="26" t="s">
+        <v>852</v>
+      </c>
+      <c r="D143" s="26" t="s">
         <v>271</v>
       </c>
-      <c r="C143" s="26" t="s">
-        <v>852</v>
-      </c>
-      <c r="D143" s="26" t="s">
+      <c r="E143" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E143" s="26" t="s">
+      <c r="F143" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="26" t="s">
         <v>285</v>
       </c>
       <c r="B144" s="26" t="s">
+        <v>853</v>
+      </c>
+      <c r="D144" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="C144" s="26" t="s">
-        <v>853</v>
-      </c>
-      <c r="D144" s="26" t="s">
+      <c r="E144" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E144" s="26" t="s">
+      <c r="F144" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="26" t="s">
         <v>327</v>
       </c>
       <c r="B145" s="26" t="s">
+        <v>854</v>
+      </c>
+      <c r="D145" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="C145" s="26" t="s">
-        <v>854</v>
-      </c>
-      <c r="D145" s="26" t="s">
+      <c r="E145" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E145" s="26" t="s">
+      <c r="F145" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="26" t="s">
         <v>538</v>
       </c>
       <c r="B146" s="26" t="s">
+        <v>855</v>
+      </c>
+      <c r="D146" s="26" t="s">
         <v>350</v>
       </c>
-      <c r="C146" s="26" t="s">
-        <v>855</v>
-      </c>
-      <c r="D146" s="26" t="s">
+      <c r="E146" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E146" s="26" t="s">
+      <c r="F146" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="26" t="s">
         <v>655</v>
       </c>
       <c r="B147" s="26" t="s">
+        <v>856</v>
+      </c>
+      <c r="D147" s="26" t="s">
         <v>396</v>
       </c>
-      <c r="C147" s="26" t="s">
-        <v>856</v>
-      </c>
-      <c r="D147" s="26" t="s">
+      <c r="E147" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E147" s="26" t="s">
+      <c r="F147" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="26" t="s">
         <v>461</v>
       </c>
       <c r="B148" s="26" t="s">
+        <v>857</v>
+      </c>
+      <c r="D148" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="C148" s="26" t="s">
-        <v>857</v>
-      </c>
-      <c r="D148" s="26" t="s">
+      <c r="E148" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E148" s="26" t="s">
+      <c r="F148" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="26" t="s">
         <v>251</v>
       </c>
       <c r="B149" s="26" t="s">
+        <v>858</v>
+      </c>
+      <c r="D149" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="C149" s="26" t="s">
-        <v>858</v>
-      </c>
-      <c r="D149" s="26" t="s">
+      <c r="E149" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E149" s="26" t="s">
+      <c r="F149" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="26" t="s">
         <v>578</v>
       </c>
       <c r="B150" s="26" t="s">
+        <v>859</v>
+      </c>
+      <c r="D150" s="26" t="s">
         <v>408</v>
       </c>
-      <c r="C150" s="26" t="s">
-        <v>859</v>
-      </c>
-      <c r="D150" s="26" t="s">
+      <c r="E150" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E150" s="26" t="s">
+      <c r="F150" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="26" t="s">
         <v>509</v>
       </c>
       <c r="B151" s="26" t="s">
+        <v>860</v>
+      </c>
+      <c r="D151" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C151" s="26" t="s">
-        <v>860</v>
-      </c>
-      <c r="D151" s="26" t="s">
+      <c r="E151" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E151" s="26" t="s">
+      <c r="F151" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B152" s="26" t="s">
+        <v>861</v>
+      </c>
+      <c r="D152" s="26" t="s">
         <v>339</v>
       </c>
-      <c r="C152" s="26" t="s">
-        <v>861</v>
-      </c>
-      <c r="D152" s="26" t="s">
+      <c r="E152" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E152" s="26" t="s">
+      <c r="F152" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="26" t="s">
         <v>144</v>
       </c>
       <c r="B153" s="26" t="s">
+        <v>862</v>
+      </c>
+      <c r="D153" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="C153" s="26" t="s">
-        <v>862</v>
-      </c>
-      <c r="D153" s="26" t="s">
+      <c r="E153" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E153" s="26" t="s">
+      <c r="F153" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="26" t="s">
         <v>437</v>
       </c>
       <c r="B154" s="26" t="s">
+        <v>863</v>
+      </c>
+      <c r="D154" s="26" t="s">
         <v>214</v>
       </c>
-      <c r="C154" s="26" t="s">
-        <v>863</v>
-      </c>
-      <c r="D154" s="26" t="s">
+      <c r="E154" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E154" s="26" t="s">
+      <c r="F154" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="26" t="s">
         <v>469</v>
       </c>
       <c r="B155" s="26" t="s">
+        <v>864</v>
+      </c>
+      <c r="D155" s="26" t="s">
         <v>292</v>
       </c>
-      <c r="C155" s="26" t="s">
-        <v>864</v>
-      </c>
-      <c r="D155" s="26" t="s">
+      <c r="E155" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E155" s="26" t="s">
+      <c r="F155" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="26" t="s">
         <v>464</v>
       </c>
       <c r="B156" s="26" t="s">
+        <v>865</v>
+      </c>
+      <c r="D156" s="26" t="s">
         <v>318</v>
       </c>
-      <c r="C156" s="26" t="s">
-        <v>865</v>
-      </c>
-      <c r="D156" s="26" t="s">
+      <c r="E156" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E156" s="26" t="s">
+      <c r="F156" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="26" t="s">
         <v>578</v>
       </c>
       <c r="B157" s="26" t="s">
+        <v>866</v>
+      </c>
+      <c r="D157" s="26" t="s">
         <v>322</v>
       </c>
-      <c r="C157" s="26" t="s">
-        <v>866</v>
-      </c>
-      <c r="D157" s="26" t="s">
+      <c r="E157" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E157" s="26" t="s">
+      <c r="F157" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="26" t="s">
         <v>92</v>
       </c>
       <c r="B158" s="26" t="s">
+        <v>867</v>
+      </c>
+      <c r="D158" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="C158" s="26" t="s">
-        <v>867</v>
-      </c>
-      <c r="D158" s="26" t="s">
+      <c r="E158" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E158" s="26" t="s">
+      <c r="F158" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="26" t="s">
         <v>5</v>
       </c>
       <c r="B159" s="26" t="s">
+        <v>868</v>
+      </c>
+      <c r="D159" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C159" s="26" t="s">
-        <v>868</v>
-      </c>
-      <c r="D159" s="26" t="s">
+      <c r="E159" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E159" s="26" t="s">
+      <c r="F159" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="26" t="s">
         <v>584</v>
       </c>
       <c r="B160" s="26" t="s">
+        <v>869</v>
+      </c>
+      <c r="D160" s="26" t="s">
         <v>286</v>
       </c>
-      <c r="C160" s="26" t="s">
-        <v>869</v>
-      </c>
-      <c r="D160" s="26" t="s">
+      <c r="E160" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E160" s="26" t="s">
+      <c r="F160" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="26" t="s">
         <v>482</v>
       </c>
       <c r="B161" s="26" t="s">
+        <v>870</v>
+      </c>
+      <c r="D161" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="C161" s="26" t="s">
-        <v>870</v>
-      </c>
-      <c r="D161" s="26" t="s">
+      <c r="E161" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E161" s="26" t="s">
+      <c r="F161" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="26" t="s">
         <v>585</v>
       </c>
       <c r="B162" s="26" t="s">
+        <v>871</v>
+      </c>
+      <c r="D162" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="C162" s="26" t="s">
-        <v>871</v>
-      </c>
-      <c r="D162" s="26" t="s">
+      <c r="E162" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E162" s="26" t="s">
+      <c r="F162" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B163" s="26" t="s">
+        <v>872</v>
+      </c>
+      <c r="D163" s="26" t="s">
         <v>369</v>
       </c>
-      <c r="C163" s="26" t="s">
-        <v>872</v>
-      </c>
-      <c r="D163" s="26" t="s">
+      <c r="E163" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E163" s="26" t="s">
+      <c r="F163" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="26" t="s">
         <v>178</v>
       </c>
       <c r="B164" s="26" t="s">
+        <v>873</v>
+      </c>
+      <c r="D164" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="C164" s="26" t="s">
-        <v>873</v>
-      </c>
-      <c r="D164" s="26" t="s">
+      <c r="E164" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E164" s="26" t="s">
+      <c r="F164" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="26" t="s">
         <v>123</v>
       </c>
       <c r="B165" s="26" t="s">
+        <v>874</v>
+      </c>
+      <c r="D165" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="C165" s="26" t="s">
-        <v>874</v>
-      </c>
-      <c r="D165" s="26" t="s">
+      <c r="E165" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E165" s="26" t="s">
+      <c r="F165" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="26" t="s">
         <v>238</v>
       </c>
       <c r="B166" s="26" t="s">
+        <v>875</v>
+      </c>
+      <c r="D166" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="C166" s="26" t="s">
-        <v>875</v>
-      </c>
-      <c r="D166" s="26" t="s">
+      <c r="E166" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E166" s="26" t="s">
+      <c r="F166" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B167" s="26" t="s">
+        <v>876</v>
+      </c>
+      <c r="D167" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C167" s="26" t="s">
-        <v>876</v>
-      </c>
-      <c r="D167" s="26" t="s">
+      <c r="E167" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E167" s="26" t="s">
+      <c r="F167" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B168" s="26" t="s">
+        <v>877</v>
+      </c>
+      <c r="D168" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="C168" s="26" t="s">
-        <v>877</v>
-      </c>
-      <c r="D168" s="26" t="s">
+      <c r="E168" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E168" s="26" t="s">
+      <c r="F168" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="26" t="s">
         <v>90</v>
       </c>
       <c r="B169" s="26" t="s">
+        <v>878</v>
+      </c>
+      <c r="D169" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="C169" s="26" t="s">
-        <v>878</v>
-      </c>
-      <c r="D169" s="26" t="s">
+      <c r="E169" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E169" s="26" t="s">
+      <c r="F169" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="26" t="s">
         <v>466</v>
       </c>
       <c r="B170" s="26" t="s">
+        <v>879</v>
+      </c>
+      <c r="D170" s="26" t="s">
         <v>315</v>
       </c>
-      <c r="C170" s="26" t="s">
-        <v>879</v>
-      </c>
-      <c r="D170" s="26" t="s">
+      <c r="E170" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E170" s="26" t="s">
+      <c r="F170" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="26" t="s">
         <v>257</v>
       </c>
       <c r="B171" s="26" t="s">
+        <v>880</v>
+      </c>
+      <c r="D171" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="C171" s="26" t="s">
-        <v>880</v>
-      </c>
-      <c r="D171" s="26" t="s">
+      <c r="E171" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E171" s="26" t="s">
+      <c r="F171" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="26" t="s">
         <v>558</v>
       </c>
       <c r="B172" s="26" t="s">
+        <v>881</v>
+      </c>
+      <c r="D172" s="26" t="s">
         <v>299</v>
       </c>
-      <c r="C172" s="26" t="s">
-        <v>881</v>
-      </c>
-      <c r="D172" s="26" t="s">
+      <c r="E172" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E172" s="26" t="s">
+      <c r="F172" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B173" s="26" t="s">
+        <v>882</v>
+      </c>
+      <c r="D173" s="26" t="s">
         <v>354</v>
       </c>
-      <c r="C173" s="26" t="s">
-        <v>882</v>
-      </c>
-      <c r="D173" s="26" t="s">
+      <c r="E173" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E173" s="26" t="s">
+      <c r="F173" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="26" t="s">
         <v>445</v>
       </c>
       <c r="B174" s="26" t="s">
+        <v>883</v>
+      </c>
+      <c r="D174" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="C174" s="26" t="s">
-        <v>883</v>
-      </c>
-      <c r="D174" s="26" t="s">
+      <c r="E174" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E174" s="26" t="s">
+      <c r="F174" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="26" t="s">
         <v>452</v>
       </c>
       <c r="B175" s="26" t="s">
+        <v>884</v>
+      </c>
+      <c r="D175" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="C175" s="26" t="s">
-        <v>884</v>
-      </c>
-      <c r="D175" s="26" t="s">
+      <c r="E175" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E175" s="26" t="s">
+      <c r="F175" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="26" t="s">
         <v>586</v>
       </c>
       <c r="B176" s="26" t="s">
+        <v>885</v>
+      </c>
+      <c r="D176" s="26" t="s">
         <v>217</v>
       </c>
-      <c r="C176" s="26" t="s">
-        <v>885</v>
-      </c>
-      <c r="D176" s="26" t="s">
+      <c r="E176" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E176" s="26" t="s">
+      <c r="F176" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="26" t="s">
         <v>210</v>
       </c>
       <c r="B177" s="26" t="s">
+        <v>886</v>
+      </c>
+      <c r="D177" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="C177" s="26" t="s">
-        <v>886</v>
-      </c>
-      <c r="D177" s="26" t="s">
+      <c r="E177" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E177" s="26" t="s">
+      <c r="F177" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="26" t="s">
         <v>668</v>
       </c>
       <c r="B178" s="26" t="s">
+        <v>887</v>
+      </c>
+      <c r="D178" s="26" t="s">
         <v>355</v>
       </c>
-      <c r="C178" s="26" t="s">
-        <v>887</v>
-      </c>
-      <c r="D178" s="26" t="s">
+      <c r="E178" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E178" s="26" t="s">
+      <c r="F178" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="26" t="s">
         <v>669</v>
       </c>
       <c r="B179" s="26" t="s">
+        <v>888</v>
+      </c>
+      <c r="D179" s="26" t="s">
         <v>356</v>
       </c>
-      <c r="C179" s="26" t="s">
-        <v>888</v>
-      </c>
-      <c r="D179" s="26" t="s">
+      <c r="E179" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E179" s="26" t="s">
+      <c r="F179" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="26" t="s">
         <v>404</v>
       </c>
       <c r="B180" s="26" t="s">
+        <v>889</v>
+      </c>
+      <c r="D180" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="C180" s="26" t="s">
-        <v>889</v>
-      </c>
-      <c r="D180" s="26" t="s">
+      <c r="E180" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E180" s="26" t="s">
+      <c r="F180" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="26" t="s">
         <v>361</v>
       </c>
       <c r="B181" s="26" t="s">
+        <v>890</v>
+      </c>
+      <c r="D181" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="C181" s="26" t="s">
-        <v>890</v>
-      </c>
-      <c r="D181" s="26" t="s">
+      <c r="E181" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E181" s="26" t="s">
+      <c r="F181" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="26" t="s">
         <v>578</v>
       </c>
       <c r="B182" s="26" t="s">
+        <v>891</v>
+      </c>
+      <c r="D182" s="26" t="s">
         <v>323</v>
       </c>
-      <c r="C182" s="26" t="s">
-        <v>891</v>
-      </c>
-      <c r="D182" s="26" t="s">
+      <c r="E182" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E182" s="26" t="s">
+      <c r="F182" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B183" s="26" t="s">
+        <v>892</v>
+      </c>
+      <c r="D183" s="26" t="s">
         <v>428</v>
       </c>
-      <c r="C183" s="26" t="s">
-        <v>892</v>
-      </c>
-      <c r="D183" s="26" t="s">
+      <c r="E183" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E183" s="26" t="s">
+      <c r="F183" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B184" s="26" t="s">
+        <v>893</v>
+      </c>
+      <c r="D184" s="26" t="s">
         <v>341</v>
       </c>
-      <c r="C184" s="26" t="s">
-        <v>893</v>
-      </c>
-      <c r="D184" s="26" t="s">
+      <c r="E184" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E184" s="26" t="s">
+      <c r="F184" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="26" t="s">
         <v>467</v>
       </c>
       <c r="B185" s="26" t="s">
+        <v>894</v>
+      </c>
+      <c r="D185" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="C185" s="26" t="s">
-        <v>894</v>
-      </c>
-      <c r="D185" s="26" t="s">
+      <c r="E185" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E185" s="26" t="s">
+      <c r="F185" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B186" s="26" t="s">
+        <v>895</v>
+      </c>
+      <c r="D186" s="26" t="s">
         <v>416</v>
       </c>
-      <c r="C186" s="26" t="s">
-        <v>895</v>
-      </c>
-      <c r="D186" s="26" t="s">
+      <c r="E186" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E186" s="26" t="s">
+      <c r="F186" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="26" t="s">
         <v>615</v>
       </c>
       <c r="B187" s="26" t="s">
+        <v>896</v>
+      </c>
+      <c r="D187" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="C187" s="26" t="s">
-        <v>896</v>
-      </c>
-      <c r="D187" s="26" t="s">
+      <c r="E187" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E187" s="26" t="s">
+      <c r="F187" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="26" t="s">
         <v>72</v>
       </c>
       <c r="B188" s="26" t="s">
+        <v>897</v>
+      </c>
+      <c r="D188" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C188" s="26" t="s">
-        <v>897</v>
-      </c>
-      <c r="D188" s="26" t="s">
+      <c r="E188" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E188" s="26" t="s">
+      <c r="F188" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="26" t="s">
         <v>447</v>
       </c>
       <c r="B189" s="26" t="s">
+        <v>898</v>
+      </c>
+      <c r="D189" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="C189" s="26" t="s">
-        <v>898</v>
-      </c>
-      <c r="D189" s="26" t="s">
+      <c r="E189" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E189" s="26" t="s">
+      <c r="F189" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="26" t="s">
         <v>463</v>
       </c>
       <c r="B190" s="26" t="s">
+        <v>899</v>
+      </c>
+      <c r="D190" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="C190" s="26" t="s">
-        <v>899</v>
-      </c>
-      <c r="D190" s="26" t="s">
+      <c r="E190" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E190" s="26" t="s">
+      <c r="F190" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="26" t="s">
         <v>388</v>
       </c>
       <c r="B191" s="26" t="s">
+        <v>900</v>
+      </c>
+      <c r="D191" s="26" t="s">
         <v>303</v>
       </c>
-      <c r="C191" s="26" t="s">
-        <v>900</v>
-      </c>
-      <c r="D191" s="26" t="s">
+      <c r="E191" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E191" s="26" t="s">
+      <c r="F191" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="26" t="s">
         <v>671</v>
       </c>
       <c r="B192" s="26" t="s">
+        <v>901</v>
+      </c>
+      <c r="D192" s="26" t="s">
         <v>332</v>
       </c>
-      <c r="C192" s="26" t="s">
-        <v>901</v>
-      </c>
-      <c r="D192" s="26" t="s">
+      <c r="E192" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E192" s="26" t="s">
+      <c r="F192" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="26" t="s">
         <v>59</v>
       </c>
       <c r="B193" s="26" t="s">
+        <v>902</v>
+      </c>
+      <c r="D193" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C193" s="26" t="s">
-        <v>902</v>
-      </c>
-      <c r="D193" s="26" t="s">
+      <c r="E193" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E193" s="26" t="s">
+      <c r="F193" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="26" t="s">
         <v>140</v>
       </c>
       <c r="B194" s="26" t="s">
+        <v>903</v>
+      </c>
+      <c r="D194" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="C194" s="26" t="s">
-        <v>903</v>
-      </c>
-      <c r="D194" s="26" t="s">
+      <c r="E194" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E194" s="26" t="s">
+      <c r="F194" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="26" t="s">
         <v>483</v>
       </c>
       <c r="B195" s="26" t="s">
+        <v>904</v>
+      </c>
+      <c r="D195" s="26" t="s">
         <v>293</v>
       </c>
-      <c r="C195" s="26" t="s">
-        <v>904</v>
-      </c>
-      <c r="D195" s="26" t="s">
+      <c r="E195" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E195" s="26" t="s">
+      <c r="F195" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="26" t="s">
         <v>561</v>
       </c>
       <c r="B196" s="26" t="s">
+        <v>905</v>
+      </c>
+      <c r="D196" s="26" t="s">
         <v>374</v>
       </c>
-      <c r="C196" s="26" t="s">
-        <v>905</v>
-      </c>
-      <c r="D196" s="26" t="s">
+      <c r="E196" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E196" s="26" t="s">
+      <c r="F196" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="26" t="s">
         <v>132</v>
       </c>
       <c r="B197" s="26" t="s">
+        <v>906</v>
+      </c>
+      <c r="D197" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="C197" s="26" t="s">
-        <v>906</v>
-      </c>
-      <c r="D197" s="26" t="s">
+      <c r="E197" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E197" s="26" t="s">
+      <c r="F197" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="26" t="s">
         <v>672</v>
       </c>
       <c r="B198" s="26" t="s">
+        <v>907</v>
+      </c>
+      <c r="D198" s="26" t="s">
         <v>423</v>
       </c>
-      <c r="C198" s="26" t="s">
-        <v>907</v>
-      </c>
-      <c r="D198" s="26" t="s">
+      <c r="E198" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E198" s="26" t="s">
+      <c r="F198" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B199" s="26" t="s">
+        <v>908</v>
+      </c>
+      <c r="D199" s="26" t="s">
         <v>383</v>
       </c>
-      <c r="C199" s="26" t="s">
-        <v>908</v>
-      </c>
-      <c r="D199" s="26" t="s">
+      <c r="E199" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E199" s="26" t="s">
+      <c r="F199" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="26" t="s">
         <v>472</v>
       </c>
       <c r="B200" s="26" t="s">
+        <v>909</v>
+      </c>
+      <c r="D200" s="26" t="s">
         <v>222</v>
       </c>
-      <c r="C200" s="26" t="s">
-        <v>909</v>
-      </c>
-      <c r="D200" s="26" t="s">
+      <c r="E200" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E200" s="26" t="s">
+      <c r="F200" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="26" t="s">
         <v>576</v>
       </c>
       <c r="B201" s="26" t="s">
+        <v>910</v>
+      </c>
+      <c r="D201" s="26" t="s">
         <v>246</v>
       </c>
-      <c r="C201" s="26" t="s">
-        <v>910</v>
-      </c>
-      <c r="D201" s="26" t="s">
+      <c r="E201" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E201" s="26" t="s">
+      <c r="F201" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="26" t="s">
         <v>575</v>
       </c>
       <c r="B202" s="26" t="s">
+        <v>911</v>
+      </c>
+      <c r="D202" s="26" t="s">
         <v>384</v>
       </c>
-      <c r="C202" s="26" t="s">
-        <v>911</v>
-      </c>
-      <c r="D202" s="26" t="s">
+      <c r="E202" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E202" s="26" t="s">
+      <c r="F202" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="26" t="s">
         <v>578</v>
       </c>
       <c r="B203" s="26" t="s">
+        <v>912</v>
+      </c>
+      <c r="D203" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="C203" s="26" t="s">
-        <v>912</v>
-      </c>
-      <c r="D203" s="26" t="s">
+      <c r="E203" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E203" s="26" t="s">
+      <c r="F203" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="26" t="s">
         <v>628</v>
       </c>
       <c r="B204" s="26" t="s">
+        <v>913</v>
+      </c>
+      <c r="D204" s="26" t="s">
         <v>295</v>
       </c>
-      <c r="C204" s="26" t="s">
-        <v>913</v>
-      </c>
-      <c r="D204" s="26" t="s">
+      <c r="E204" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E204" s="26" t="s">
+      <c r="F204" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="26" t="s">
         <v>152</v>
       </c>
       <c r="B205" s="26" t="s">
+        <v>914</v>
+      </c>
+      <c r="D205" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="C205" s="26" t="s">
-        <v>914</v>
-      </c>
-      <c r="D205" s="26" t="s">
+      <c r="E205" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E205" s="26" t="s">
+      <c r="F205" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B206" s="26" t="s">
+        <v>915</v>
+      </c>
+      <c r="D206" s="26" t="s">
         <v>386</v>
       </c>
-      <c r="C206" s="26" t="s">
-        <v>915</v>
-      </c>
-      <c r="D206" s="26" t="s">
+      <c r="E206" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E206" s="26" t="s">
+      <c r="F206" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="26" t="s">
         <v>73</v>
       </c>
       <c r="B207" s="26" t="s">
+        <v>916</v>
+      </c>
+      <c r="D207" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="C207" s="26" t="s">
-        <v>916</v>
-      </c>
-      <c r="D207" s="26" t="s">
+      <c r="E207" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E207" s="26" t="s">
+      <c r="F207" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="26" t="s">
         <v>618</v>
       </c>
       <c r="B208" s="26" t="s">
+        <v>917</v>
+      </c>
+      <c r="D208" s="26" t="s">
         <v>321</v>
       </c>
-      <c r="C208" s="26" t="s">
-        <v>917</v>
-      </c>
-      <c r="D208" s="26" t="s">
+      <c r="E208" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E208" s="26" t="s">
+      <c r="F208" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="26" t="s">
         <v>578</v>
       </c>
       <c r="B209" s="26" t="s">
+        <v>918</v>
+      </c>
+      <c r="D209" s="26" t="s">
         <v>237</v>
       </c>
-      <c r="C209" s="26" t="s">
-        <v>918</v>
-      </c>
-      <c r="D209" s="26" t="s">
+      <c r="E209" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E209" s="26" t="s">
+      <c r="F209" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="26" t="s">
         <v>628</v>
       </c>
       <c r="B210" s="26" t="s">
+        <v>919</v>
+      </c>
+      <c r="D210" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="C210" s="26" t="s">
-        <v>919</v>
-      </c>
-      <c r="D210" s="26" t="s">
+      <c r="E210" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E210" s="26" t="s">
+      <c r="F210" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="26" t="s">
         <v>49</v>
       </c>
       <c r="B211" s="26" t="s">
+        <v>920</v>
+      </c>
+      <c r="D211" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="C211" s="26" t="s">
-        <v>920</v>
-      </c>
-      <c r="D211" s="26" t="s">
+      <c r="E211" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E211" s="26" t="s">
+      <c r="F211" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="26" t="s">
         <v>681</v>
       </c>
       <c r="B212" s="26" t="s">
+        <v>921</v>
+      </c>
+      <c r="D212" s="26" t="s">
         <v>429</v>
       </c>
-      <c r="C212" s="26" t="s">
-        <v>921</v>
-      </c>
-      <c r="D212" s="26" t="s">
+      <c r="E212" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E212" s="26" t="s">
+      <c r="F212" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="26" t="s">
         <v>682</v>
       </c>
       <c r="B213" s="26" t="s">
+        <v>922</v>
+      </c>
+      <c r="D213" s="26" t="s">
         <v>417</v>
       </c>
-      <c r="C213" s="26" t="s">
-        <v>922</v>
-      </c>
-      <c r="D213" s="26" t="s">
+      <c r="E213" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E213" s="26" t="s">
+      <c r="F213" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="26" t="s">
         <v>223</v>
       </c>
       <c r="B214" s="26" t="s">
+        <v>923</v>
+      </c>
+      <c r="D214" s="26" t="s">
         <v>224</v>
       </c>
-      <c r="C214" s="26" t="s">
-        <v>923</v>
-      </c>
-      <c r="D214" s="26" t="s">
+      <c r="E214" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E214" s="26" t="s">
+      <c r="F214" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="26" t="s">
         <v>448</v>
       </c>
       <c r="B215" s="26" t="s">
+        <v>924</v>
+      </c>
+      <c r="D215" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="C215" s="26" t="s">
-        <v>924</v>
-      </c>
-      <c r="D215" s="26" t="s">
+      <c r="E215" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E215" s="26" t="s">
+      <c r="F215" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="26" t="s">
         <v>547</v>
       </c>
       <c r="B216" s="26" t="s">
+        <v>925</v>
+      </c>
+      <c r="D216" s="26" t="s">
         <v>357</v>
       </c>
-      <c r="C216" s="26" t="s">
-        <v>925</v>
-      </c>
-      <c r="D216" s="26" t="s">
+      <c r="E216" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E216" s="26" t="s">
+      <c r="F216" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="26" t="s">
         <v>167</v>
       </c>
       <c r="B217" s="26" t="s">
+        <v>926</v>
+      </c>
+      <c r="D217" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="C217" s="26" t="s">
-        <v>926</v>
-      </c>
-      <c r="D217" s="26" t="s">
+      <c r="E217" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E217" s="26" t="s">
+      <c r="F217" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="26" t="s">
         <v>434</v>
       </c>
       <c r="B218" s="26" t="s">
+        <v>927</v>
+      </c>
+      <c r="D218" s="26" t="s">
         <v>320</v>
       </c>
-      <c r="C218" s="26" t="s">
-        <v>927</v>
-      </c>
-      <c r="D218" s="26" t="s">
+      <c r="E218" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E218" s="26" t="s">
+      <c r="F218" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="26" t="s">
         <v>56</v>
       </c>
       <c r="B219" s="26" t="s">
+        <v>928</v>
+      </c>
+      <c r="D219" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="C219" s="26" t="s">
-        <v>928</v>
-      </c>
-      <c r="D219" s="26" t="s">
+      <c r="E219" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E219" s="26" t="s">
+      <c r="F219" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="26" t="s">
         <v>685</v>
       </c>
       <c r="B220" s="26" t="s">
+        <v>929</v>
+      </c>
+      <c r="D220" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="C220" s="26" t="s">
-        <v>929</v>
-      </c>
-      <c r="D220" s="26" t="s">
+      <c r="E220" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E220" s="26" t="s">
+      <c r="F220" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="26" t="s">
         <v>63</v>
       </c>
       <c r="B221" s="26" t="s">
+        <v>930</v>
+      </c>
+      <c r="D221" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="C221" s="26" t="s">
-        <v>930</v>
-      </c>
-      <c r="D221" s="26" t="s">
+      <c r="E221" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E221" s="26" t="s">
+      <c r="F221" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="26" t="s">
         <v>424</v>
       </c>
       <c r="B222" s="26" t="s">
+        <v>931</v>
+      </c>
+      <c r="D222" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="C222" s="26" t="s">
-        <v>931</v>
-      </c>
-      <c r="D222" s="26" t="s">
+      <c r="E222" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E222" s="26" t="s">
+      <c r="F222" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="26" t="s">
         <v>686</v>
       </c>
       <c r="B223" s="26" t="s">
+        <v>932</v>
+      </c>
+      <c r="D223" s="26" t="s">
         <v>398</v>
       </c>
-      <c r="C223" s="26" t="s">
-        <v>932</v>
-      </c>
-      <c r="D223" s="26" t="s">
+      <c r="E223" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E223" s="26" t="s">
+      <c r="F223" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="26" t="s">
         <v>99</v>
       </c>
       <c r="B224" s="26" t="s">
+        <v>933</v>
+      </c>
+      <c r="D224" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="C224" s="26" t="s">
-        <v>933</v>
-      </c>
-      <c r="D224" s="26" t="s">
+      <c r="E224" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E224" s="26" t="s">
+      <c r="F224" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="26" t="s">
         <v>456</v>
       </c>
       <c r="B225" s="26" t="s">
+        <v>934</v>
+      </c>
+      <c r="D225" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="C225" s="26" t="s">
-        <v>934</v>
-      </c>
-      <c r="D225" s="26" t="s">
+      <c r="E225" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E225" s="26" t="s">
+      <c r="F225" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B226" s="26" t="s">
+        <v>935</v>
+      </c>
+      <c r="D226" s="26" t="s">
         <v>342</v>
       </c>
-      <c r="C226" s="26" t="s">
-        <v>935</v>
-      </c>
-      <c r="D226" s="26" t="s">
+      <c r="E226" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E226" s="26" t="s">
+      <c r="F226" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="26" t="s">
         <v>148</v>
       </c>
       <c r="B227" s="26" t="s">
+        <v>936</v>
+      </c>
+      <c r="D227" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="C227" s="26" t="s">
-        <v>936</v>
-      </c>
-      <c r="D227" s="26" t="s">
+      <c r="E227" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E227" s="26" t="s">
+      <c r="F227" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="26" t="s">
         <v>309</v>
       </c>
       <c r="B228" s="26" t="s">
+        <v>937</v>
+      </c>
+      <c r="D228" s="26" t="s">
         <v>310</v>
       </c>
-      <c r="C228" s="26" t="s">
-        <v>937</v>
-      </c>
-      <c r="D228" s="26" t="s">
+      <c r="E228" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E228" s="26" t="s">
+      <c r="F228" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="26" t="s">
         <v>549</v>
       </c>
       <c r="B229" s="26" t="s">
+        <v>938</v>
+      </c>
+      <c r="D229" s="26" t="s">
         <v>289</v>
       </c>
-      <c r="C229" s="26" t="s">
-        <v>938</v>
-      </c>
-      <c r="D229" s="26" t="s">
+      <c r="E229" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E229" s="26" t="s">
+      <c r="F229" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="26" t="s">
         <v>620</v>
       </c>
       <c r="B230" s="26" t="s">
+        <v>939</v>
+      </c>
+      <c r="D230" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="C230" s="26" t="s">
-        <v>939</v>
-      </c>
-      <c r="D230" s="26" t="s">
+      <c r="E230" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E230" s="26" t="s">
+      <c r="F230" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="26" t="s">
         <v>690</v>
       </c>
       <c r="B231" s="26" t="s">
+        <v>940</v>
+      </c>
+      <c r="D231" s="26" t="s">
         <v>333</v>
       </c>
-      <c r="C231" s="26" t="s">
-        <v>940</v>
-      </c>
-      <c r="D231" s="26" t="s">
+      <c r="E231" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E231" s="26" t="s">
+      <c r="F231" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B232" s="26" t="s">
+        <v>941</v>
+      </c>
+      <c r="D232" s="26" t="s">
         <v>358</v>
       </c>
-      <c r="C232" s="26" t="s">
-        <v>941</v>
-      </c>
-      <c r="D232" s="26" t="s">
+      <c r="E232" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E232" s="26" t="s">
+      <c r="F232" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B233" s="26" t="s">
+        <v>942</v>
+      </c>
+      <c r="D233" s="26" t="s">
         <v>343</v>
       </c>
-      <c r="C233" s="26" t="s">
-        <v>942</v>
-      </c>
-      <c r="D233" s="26" t="s">
+      <c r="E233" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E233" s="26" t="s">
+      <c r="F233" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B234" s="26" t="s">
+        <v>943</v>
+      </c>
+      <c r="D234" s="26" t="s">
         <v>344</v>
       </c>
-      <c r="C234" s="26" t="s">
-        <v>943</v>
-      </c>
-      <c r="D234" s="26" t="s">
+      <c r="E234" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E234" s="26" t="s">
+      <c r="F234" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="26" t="s">
         <v>68</v>
       </c>
       <c r="B235" s="26" t="s">
+        <v>944</v>
+      </c>
+      <c r="D235" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="C235" s="26" t="s">
-        <v>944</v>
-      </c>
-      <c r="D235" s="26" t="s">
+      <c r="E235" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E235" s="26" t="s">
+      <c r="F235" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="26" t="s">
         <v>170</v>
       </c>
       <c r="B236" s="26" t="s">
+        <v>945</v>
+      </c>
+      <c r="D236" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="C236" s="26" t="s">
-        <v>945</v>
-      </c>
-      <c r="D236" s="26" t="s">
+      <c r="E236" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E236" s="26" t="s">
+      <c r="F236" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="26" t="s">
         <v>68</v>
       </c>
       <c r="B237" s="26" t="s">
+        <v>946</v>
+      </c>
+      <c r="D237" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="C237" s="26" t="s">
-        <v>946</v>
-      </c>
-      <c r="D237" s="26" t="s">
+      <c r="E237" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E237" s="26" t="s">
+      <c r="F237" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="26" t="s">
         <v>592</v>
       </c>
       <c r="B238" s="26" t="s">
+        <v>947</v>
+      </c>
+      <c r="D238" s="26" t="s">
         <v>334</v>
       </c>
-      <c r="C238" s="26" t="s">
-        <v>947</v>
-      </c>
-      <c r="D238" s="26" t="s">
+      <c r="E238" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E238" s="26" t="s">
+      <c r="F238" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="26" t="s">
         <v>290</v>
       </c>
       <c r="B239" s="26" t="s">
+        <v>948</v>
+      </c>
+      <c r="D239" s="26" t="s">
         <v>226</v>
       </c>
-      <c r="C239" s="26" t="s">
-        <v>948</v>
-      </c>
-      <c r="D239" s="26" t="s">
+      <c r="E239" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E239" s="26" t="s">
+      <c r="F239" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="26" t="s">
         <v>294</v>
       </c>
       <c r="B240" s="26" t="s">
+        <v>949</v>
+      </c>
+      <c r="D240" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="C240" s="26" t="s">
-        <v>949</v>
-      </c>
-      <c r="D240" s="26" t="s">
+      <c r="E240" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E240" s="26" t="s">
+      <c r="F240" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B241" s="26" t="s">
+        <v>950</v>
+      </c>
+      <c r="D241" s="26" t="s">
         <v>345</v>
       </c>
-      <c r="C241" s="26" t="s">
-        <v>950</v>
-      </c>
-      <c r="D241" s="26" t="s">
+      <c r="E241" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E241" s="26" t="s">
+      <c r="F241" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="26" t="s">
         <v>480</v>
       </c>
       <c r="B242" s="26" t="s">
+        <v>951</v>
+      </c>
+      <c r="D242" s="26" t="s">
         <v>370</v>
       </c>
-      <c r="C242" s="26" t="s">
-        <v>951</v>
-      </c>
-      <c r="D242" s="26" t="s">
+      <c r="E242" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E242" s="26" t="s">
+      <c r="F242" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="26" t="s">
         <v>288</v>
       </c>
       <c r="B243" s="26" t="s">
+        <v>952</v>
+      </c>
+      <c r="D243" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="C243" s="26" t="s">
-        <v>952</v>
-      </c>
-      <c r="D243" s="26" t="s">
+      <c r="E243" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E243" s="26" t="s">
+      <c r="F243" s="26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="26" t="s">
         <v>578</v>
       </c>
       <c r="B244" s="26" t="s">
+        <v>953</v>
+      </c>
+      <c r="D244" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="C244" s="26" t="s">
-        <v>953</v>
-      </c>
-      <c r="D244" s="26" t="s">
+      <c r="E244" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E244" s="26" t="s">
+      <c r="F244" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="26" t="s">
         <v>37</v>
       </c>
       <c r="B245" s="26" t="s">
+        <v>954</v>
+      </c>
+      <c r="D245" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C245" s="26" t="s">
-        <v>954</v>
-      </c>
-      <c r="D245" s="26" t="s">
+      <c r="E245" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E245" s="26" t="s">
+      <c r="F245" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="26" t="s">
         <v>623</v>
       </c>
       <c r="B246" s="26" t="s">
+        <v>955</v>
+      </c>
+      <c r="D246" s="26" t="s">
         <v>225</v>
       </c>
-      <c r="C246" s="26" t="s">
-        <v>955</v>
-      </c>
-      <c r="D246" s="26" t="s">
+      <c r="E246" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E246" s="26" t="s">
+      <c r="F246" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B247" s="26" t="s">
+        <v>956</v>
+      </c>
+      <c r="D247" s="26" t="s">
         <v>418</v>
       </c>
-      <c r="C247" s="26" t="s">
-        <v>956</v>
-      </c>
-      <c r="D247" s="26" t="s">
+      <c r="E247" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E247" s="26" t="s">
+      <c r="F247" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="26" t="s">
         <v>149</v>
       </c>
       <c r="B248" s="26" t="s">
+        <v>957</v>
+      </c>
+      <c r="D248" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="C248" s="26" t="s">
-        <v>957</v>
-      </c>
-      <c r="D248" s="26" t="s">
+      <c r="E248" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E248" s="26" t="s">
+      <c r="F248" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="26" t="s">
         <v>460</v>
       </c>
       <c r="B249" s="26" t="s">
+        <v>958</v>
+      </c>
+      <c r="D249" s="26" t="s">
         <v>375</v>
       </c>
-      <c r="C249" s="26" t="s">
-        <v>958</v>
-      </c>
-      <c r="D249" s="26" t="s">
+      <c r="E249" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E249" s="26" t="s">
+      <c r="F249" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="26" t="s">
         <v>151</v>
       </c>
       <c r="B250" s="26" t="s">
+        <v>959</v>
+      </c>
+      <c r="D250" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="C250" s="26" t="s">
-        <v>959</v>
-      </c>
-      <c r="D250" s="26" t="s">
+      <c r="E250" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E250" s="26" t="s">
+      <c r="F250" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="26" t="s">
         <v>511</v>
       </c>
       <c r="B251" s="26" t="s">
+        <v>960</v>
+      </c>
+      <c r="D251" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="C251" s="26" t="s">
-        <v>960</v>
-      </c>
-      <c r="D251" s="26" t="s">
+      <c r="E251" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E251" s="26" t="s">
+      <c r="F251" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="26" t="s">
         <v>512</v>
       </c>
       <c r="B252" s="26" t="s">
+        <v>961</v>
+      </c>
+      <c r="D252" s="26" t="s">
         <v>376</v>
       </c>
-      <c r="C252" s="26" t="s">
-        <v>961</v>
-      </c>
-      <c r="D252" s="26" t="s">
+      <c r="E252" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E252" s="26" t="s">
+      <c r="F252" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="26" t="s">
         <v>598</v>
       </c>
       <c r="B253" s="26" t="s">
+        <v>962</v>
+      </c>
+      <c r="D253" s="26" t="s">
         <v>387</v>
       </c>
-      <c r="C253" s="26" t="s">
-        <v>962</v>
-      </c>
-      <c r="D253" s="26" t="s">
+      <c r="E253" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E253" s="26" t="s">
+      <c r="F253" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="26" t="s">
         <v>705</v>
       </c>
       <c r="B254" s="26" t="s">
+        <v>963</v>
+      </c>
+      <c r="D254" s="26" t="s">
         <v>215</v>
       </c>
-      <c r="C254" s="26" t="s">
-        <v>963</v>
-      </c>
-      <c r="D254" s="26" t="s">
+      <c r="E254" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E254" s="26" t="s">
+      <c r="F254" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="26" t="s">
         <v>578</v>
       </c>
       <c r="B255" s="26" t="s">
+        <v>964</v>
+      </c>
+      <c r="D255" s="26" t="s">
         <v>410</v>
       </c>
-      <c r="C255" s="26" t="s">
-        <v>964</v>
-      </c>
-      <c r="D255" s="26" t="s">
+      <c r="E255" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E255" s="26" t="s">
+      <c r="F255" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="26" t="s">
         <v>459</v>
       </c>
       <c r="B256" s="26" t="s">
+        <v>965</v>
+      </c>
+      <c r="D256" s="26" t="s">
         <v>297</v>
       </c>
-      <c r="C256" s="26" t="s">
-        <v>965</v>
-      </c>
-      <c r="D256" s="26" t="s">
+      <c r="E256" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E256" s="26" t="s">
+      <c r="F256" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="26" t="s">
         <v>137</v>
       </c>
       <c r="B257" s="26" t="s">
+        <v>966</v>
+      </c>
+      <c r="D257" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="C257" s="26" t="s">
-        <v>966</v>
-      </c>
-      <c r="D257" s="26" t="s">
+      <c r="E257" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E257" s="26" t="s">
+      <c r="F257" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="26" t="s">
         <v>442</v>
       </c>
       <c r="B258" s="26" t="s">
+        <v>967</v>
+      </c>
+      <c r="D258" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="C258" s="26" t="s">
-        <v>967</v>
-      </c>
-      <c r="D258" s="26" t="s">
+      <c r="E258" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E258" s="26" t="s">
+      <c r="F258" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="26" t="s">
         <v>578</v>
       </c>
       <c r="B259" s="26" t="s">
+        <v>968</v>
+      </c>
+      <c r="D259" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C259" s="26" t="s">
-        <v>968</v>
-      </c>
-      <c r="D259" s="26" t="s">
+      <c r="E259" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E259" s="26" t="s">
+      <c r="F259" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="26" t="s">
         <v>628</v>
       </c>
       <c r="B260" s="26" t="s">
+        <v>969</v>
+      </c>
+      <c r="D260" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="C260" s="26" t="s">
-        <v>969</v>
-      </c>
-      <c r="D260" s="26" t="s">
+      <c r="E260" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E260" s="26" t="s">
+      <c r="F260" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="26" t="s">
         <v>578</v>
       </c>
       <c r="B261" s="26" t="s">
+        <v>970</v>
+      </c>
+      <c r="D261" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="C261" s="26" t="s">
-        <v>970</v>
-      </c>
-      <c r="D261" s="26" t="s">
+      <c r="E261" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E261" s="26" t="s">
+      <c r="F261" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="26" t="s">
         <v>704</v>
       </c>
       <c r="B262" s="26" t="s">
+        <v>971</v>
+      </c>
+      <c r="D262" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="C262" s="26" t="s">
-        <v>971</v>
-      </c>
-      <c r="D262" s="26" t="s">
+      <c r="E262" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E262" s="26" t="s">
+      <c r="F262" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B263" s="26" t="s">
+        <v>972</v>
+      </c>
+      <c r="D263" s="26" t="s">
         <v>403</v>
       </c>
-      <c r="C263" s="26" t="s">
-        <v>972</v>
-      </c>
-      <c r="D263" s="26" t="s">
+      <c r="E263" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E263" s="26" t="s">
+      <c r="F263" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="26" t="s">
         <v>578</v>
       </c>
       <c r="B264" s="26" t="s">
+        <v>973</v>
+      </c>
+      <c r="D264" s="26" t="s">
         <v>411</v>
       </c>
-      <c r="C264" s="26" t="s">
-        <v>973</v>
-      </c>
-      <c r="D264" s="26" t="s">
+      <c r="E264" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E264" s="26" t="s">
+      <c r="F264" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="26" t="s">
         <v>694</v>
       </c>
       <c r="B265" s="26" t="s">
+        <v>974</v>
+      </c>
+      <c r="D265" s="26" t="s">
         <v>326</v>
       </c>
-      <c r="C265" s="26" t="s">
-        <v>974</v>
-      </c>
-      <c r="D265" s="26" t="s">
+      <c r="E265" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E265" s="26" t="s">
+      <c r="F265" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="26" t="s">
         <v>696</v>
       </c>
       <c r="B266" s="26" t="s">
+        <v>975</v>
+      </c>
+      <c r="D266" s="26" t="s">
         <v>430</v>
       </c>
-      <c r="C266" s="26" t="s">
-        <v>975</v>
-      </c>
-      <c r="D266" s="26" t="s">
+      <c r="E266" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E266" s="26" t="s">
+      <c r="F266" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="26" t="s">
         <v>628</v>
       </c>
       <c r="B267" s="26" t="s">
+        <v>976</v>
+      </c>
+      <c r="D267" s="26" t="s">
         <v>291</v>
       </c>
-      <c r="C267" s="26" t="s">
-        <v>976</v>
-      </c>
-      <c r="D267" s="26" t="s">
+      <c r="E267" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E267" s="26" t="s">
+      <c r="F267" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="26" t="s">
         <v>198</v>
       </c>
       <c r="B268" s="26" t="s">
+        <v>977</v>
+      </c>
+      <c r="D268" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="C268" s="26" t="s">
-        <v>977</v>
-      </c>
-      <c r="D268" s="26" t="s">
+      <c r="E268" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E268" s="26" t="s">
+      <c r="F268" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="26" t="s">
         <v>628</v>
       </c>
       <c r="B269" s="26" t="s">
+        <v>978</v>
+      </c>
+      <c r="D269" s="26" t="s">
         <v>249</v>
       </c>
-      <c r="C269" s="26" t="s">
-        <v>978</v>
-      </c>
-      <c r="D269" s="26" t="s">
+      <c r="E269" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="E269" s="26" t="s">
+      <c r="F269" s="26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="26" t="s">
         <v>709</v>
       </c>
       <c r="B270" s="26" t="s">
+        <v>979</v>
+      </c>
+      <c r="D270" s="26" t="s">
         <v>352</v>
       </c>
-      <c r="C270" s="26" t="s">
-        <v>979</v>
-      </c>
-      <c r="D270" s="26" t="s">
+      <c r="E270" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E270" s="26" t="s">
+      <c r="F270" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="26" t="s">
         <v>700</v>
       </c>
       <c r="B271" s="26" t="s">
+        <v>980</v>
+      </c>
+      <c r="D271" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="C271" s="26" t="s">
-        <v>980</v>
-      </c>
-      <c r="D271" s="26" t="s">
+      <c r="E271" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="E271" s="26" t="s">
+      <c r="F271" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B272" s="26" t="s">
+        <v>981</v>
+      </c>
+      <c r="D272" s="26" t="s">
         <v>359</v>
       </c>
-      <c r="C272" s="26" t="s">
-        <v>981</v>
-      </c>
-      <c r="D272" s="26" t="s">
+      <c r="E272" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E272" s="26" t="s">
+      <c r="F272" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="26" t="s">
         <v>701</v>
       </c>
       <c r="B273" s="26" t="s">
+        <v>982</v>
+      </c>
+      <c r="D273" s="26" t="s">
         <v>367</v>
       </c>
-      <c r="C273" s="26" t="s">
-        <v>982</v>
-      </c>
-      <c r="D273" s="26" t="s">
+      <c r="E273" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E273" s="26" t="s">
+      <c r="F273" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="26" t="s">
         <v>702</v>
       </c>
       <c r="B274" s="26" t="s">
+        <v>983</v>
+      </c>
+      <c r="D274" s="26" t="s">
         <v>389</v>
       </c>
-      <c r="C274" s="26" t="s">
-        <v>983</v>
-      </c>
-      <c r="D274" s="26" t="s">
+      <c r="E274" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E274" s="26" t="s">
+      <c r="F274" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="26" t="s">
         <v>479</v>
       </c>
       <c r="B275" s="26" t="s">
+        <v>984</v>
+      </c>
+      <c r="D275" s="26" t="s">
         <v>360</v>
       </c>
-      <c r="C275" s="26" t="s">
-        <v>984</v>
-      </c>
-      <c r="D275" s="26" t="s">
+      <c r="E275" s="26" t="s">
         <v>338</v>
       </c>
-      <c r="E275" s="26" t="s">
+      <c r="F275" s="26" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="26" t="s">
         <v>570</v>
       </c>
       <c r="B276" s="26" t="s">
+        <v>985</v>
+      </c>
+      <c r="D276" s="26" t="s">
         <v>377</v>
       </c>
-      <c r="C276" s="26" t="s">
-        <v>985</v>
-      </c>
-      <c r="D276" s="26" t="s">
+      <c r="E276" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E276" s="26" t="s">
+      <c r="F276" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="26" t="s">
         <v>101</v>
       </c>
       <c r="B277" s="26" t="s">
+        <v>986</v>
+      </c>
+      <c r="D277" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="C277" s="26" t="s">
-        <v>986</v>
-      </c>
-      <c r="D277" s="26" t="s">
+      <c r="E277" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E277" s="26" t="s">
+      <c r="F277" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="26" t="s">
         <v>298</v>
       </c>
       <c r="B278" s="26" t="s">
+        <v>987</v>
+      </c>
+      <c r="D278" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="C278" s="26" t="s">
-        <v>987</v>
-      </c>
-      <c r="D278" s="26" t="s">
+      <c r="E278" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E278" s="26" t="s">
+      <c r="F278" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="26" t="s">
         <v>201</v>
       </c>
       <c r="B279" s="26" t="s">
+        <v>988</v>
+      </c>
+      <c r="D279" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C279" s="26" t="s">
-        <v>988</v>
-      </c>
-      <c r="D279" s="26" t="s">
+      <c r="E279" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="E279" s="26" t="s">
+      <c r="F279" s="26" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="26" t="s">
         <v>594</v>
       </c>
       <c r="B280" s="26" t="s">
+        <v>989</v>
+      </c>
+      <c r="D280" s="26" t="s">
         <v>287</v>
       </c>
-      <c r="C280" s="26" t="s">
-        <v>989</v>
-      </c>
-      <c r="D280" s="26" t="s">
+      <c r="E280" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E280" s="26" t="s">
+      <c r="F280" s="26" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="26" t="s">
         <v>107</v>
       </c>
       <c r="B281" s="26" t="s">
+        <v>990</v>
+      </c>
+      <c r="D281" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="C281" s="26" t="s">
-        <v>990</v>
-      </c>
-      <c r="D281" s="26" t="s">
+      <c r="E281" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E281" s="26" t="s">
+      <c r="F281" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="26" t="s">
         <v>557</v>
       </c>
       <c r="B282" s="26" t="s">
+        <v>991</v>
+      </c>
+      <c r="D282" s="26" t="s">
         <v>431</v>
       </c>
-      <c r="C282" s="26" t="s">
-        <v>991</v>
-      </c>
-      <c r="D282" s="26" t="s">
+      <c r="E282" s="26" t="s">
         <v>710</v>
       </c>
-      <c r="E282" s="26" t="s">
+      <c r="F282" s="26" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="26" t="s">
         <v>435</v>
       </c>
       <c r="B283" s="26" t="s">
+        <v>992</v>
+      </c>
+      <c r="D283" s="26" t="s">
         <v>278</v>
       </c>
-      <c r="C283" s="26" t="s">
-        <v>992</v>
-      </c>
-      <c r="D283" s="26" t="s">
+      <c r="E283" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E283" s="26" t="s">
+      <c r="F283" s="26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="26" t="s">
         <v>439</v>
       </c>
       <c r="B284" s="26" t="s">
+        <v>993</v>
+      </c>
+      <c r="D284" s="26" t="s">
         <v>203</v>
       </c>
-      <c r="C284" s="26" t="s">
-        <v>993</v>
-      </c>
-      <c r="D284" s="26" t="s">
+      <c r="E284" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E284" s="26" t="s">
+      <c r="F284" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="26" t="s">
         <v>999</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="26" t="s">
         <v>999</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="26" t="s">
         <v>999</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="26" t="s">
         <v>999</v>
       </c>
@@ -40891,1718 +40916,6 @@
         <v>999</v>
       </c>
     </row>
-    <row r="305" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="306" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="307" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="308" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="309" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="310" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="311" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="312" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="313" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="314" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="315" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="316" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="317" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="318" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="319" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="320" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="321" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="322" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="323" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="324" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="325" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="326" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="327" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="328" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="329" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="330" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="331" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="332" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="333" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="334" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="335" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="336" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="337" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="338" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="339" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="340" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="341" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="342" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="343" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="344" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="345" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="346" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="347" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="348" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="349" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="350" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="351" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="352" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="353" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="354" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="355" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="356" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="357" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="358" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="359" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="360" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="361" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="362" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="363" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="364" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="365" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="366" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="367" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="368" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="369" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="370" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="371" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="372" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="373" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="374" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="375" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="376" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="377" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="378" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="379" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="380" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="381" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="382" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="383" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="384" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="385" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="386" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="387" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="388" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="389" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="390" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="391" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="392" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="393" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="394" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="395" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="396" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="397" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="398" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="399" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="400" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="401" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="402" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="403" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="404" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="405" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="406" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="407" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="408" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="409" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="410" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="411" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="412" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="413" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="414" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="415" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="416" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="417" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="418" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="419" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="420" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="421" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="422" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="423" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="424" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="425" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="426" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="427" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="428" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="429" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="430" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="431" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="432" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="433" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="434" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="435" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="436" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="437" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="438" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="439" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="440" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="441" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="442" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="443" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="444" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="445" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="446" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="447" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="448" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="449" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="450" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="451" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="452" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="453" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="454" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="455" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="456" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="457" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="458" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="459" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="460" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="461" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="462" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="463" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="464" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="465" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="466" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="467" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="468" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="469" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="470" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="471" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="472" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="473" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="474" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="475" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="476" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="477" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="478" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="479" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="480" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="481" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="482" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="483" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="484" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="485" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="486" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="487" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="488" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="489" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="490" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="491" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="492" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="493" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="494" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="495" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="496" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="497" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="498" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="499" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="500" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="501" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="502" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="503" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="504" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="505" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="506" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="507" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="508" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="509" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="510" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="511" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="512" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="513" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="514" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="515" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="516" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="517" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="518" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="519" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="520" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="521" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="522" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="523" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="524" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="525" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="526" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="527" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="528" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="529" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="530" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="531" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="532" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="533" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="534" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="535" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="536" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="537" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="538" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="539" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="540" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="541" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="542" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="543" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="544" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="545" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="546" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="547" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="548" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="549" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="550" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="551" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="552" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="553" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="554" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="555" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="556" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="557" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="558" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="559" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="560" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="561" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="562" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="563" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="564" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="565" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="566" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="567" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="568" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="569" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="570" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="571" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="572" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="573" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="574" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="575" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="576" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="577" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="578" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="579" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="580" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="581" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="582" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="583" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="584" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="585" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="586" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="587" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="588" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="589" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="590" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="591" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="592" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="593" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="594" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="595" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="596" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="597" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="598" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="599" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="600" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="601" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="602" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="603" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="604" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="605" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="606" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="607" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="608" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="609" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="610" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="611" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="612" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="613" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="614" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="615" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="616" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="617" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="618" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="619" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="620" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="621" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="622" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="623" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="624" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="625" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="626" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="627" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="628" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="629" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="630" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="631" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="632" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="633" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="634" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="635" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="636" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="637" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="638" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="639" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="640" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="641" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="642" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="643" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="644" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="645" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="646" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="647" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="648" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="649" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="650" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="651" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="652" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="653" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="654" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="655" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="656" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="657" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="658" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="659" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="660" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="661" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="662" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="663" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="664" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="665" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="666" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="667" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="668" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="669" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="670" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="671" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="672" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="673" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="674" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="675" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="676" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="677" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="678" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="679" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="680" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="681" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="682" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="683" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="684" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="685" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="686" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="687" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="688" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="689" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="690" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="691" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="692" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="693" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="694" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="695" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="696" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="697" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="698" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="699" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="700" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="701" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="702" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="703" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="704" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="705" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="706" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="707" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="708" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="709" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="710" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="711" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="712" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="713" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="714" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="715" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="716" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="717" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="718" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="719" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="720" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="721" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="722" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="723" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="724" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="725" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="726" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="727" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="728" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="729" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="730" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="731" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="732" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="733" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="734" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="735" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="736" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="737" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="738" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="739" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="740" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="741" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="742" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="743" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="744" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="745" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="746" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="747" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="748" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="749" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="750" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="751" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="752" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="753" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="754" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="755" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="756" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="757" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="758" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="759" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="760" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="761" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="762" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="763" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="764" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="765" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="766" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="767" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="768" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="769" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="770" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="771" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="772" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="773" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="774" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="775" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="776" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="777" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="778" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="779" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="780" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="781" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="782" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="783" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="784" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="785" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="786" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="787" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="788" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="789" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="790" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="791" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="792" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="793" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="794" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="795" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="796" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="797" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="798" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="799" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="800" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="801" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="802" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="803" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="804" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="805" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="806" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="807" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="808" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="809" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="810" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="811" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="812" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="813" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="814" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="815" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="816" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="817" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="818" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="819" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="820" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="821" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="822" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="823" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="824" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="825" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="826" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="827" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="828" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="829" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="830" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="831" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="832" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="833" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="834" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="835" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="836" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="837" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="838" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="839" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="840" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="841" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="842" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="843" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="844" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="845" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="846" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="847" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="848" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="849" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="850" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="851" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="852" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="853" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="854" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="855" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="856" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="857" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="858" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="859" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="860" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="861" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="862" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="863" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="864" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="865" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="866" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="867" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="868" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="869" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="870" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="871" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="872" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="873" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="874" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="875" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="876" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="877" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="878" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="879" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="880" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="881" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="882" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="883" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="884" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="885" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="886" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="887" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="888" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="889" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="890" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="891" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="892" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="893" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="894" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="895" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="896" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="897" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="898" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="899" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="900" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="901" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="902" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="903" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="904" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="905" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="906" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="907" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="908" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="909" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="910" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="911" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="912" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="913" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="914" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="915" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="916" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="917" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="918" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="919" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="920" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="921" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="922" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="923" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="924" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="925" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="926" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="927" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="928" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="929" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="930" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="931" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="932" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="933" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="934" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="935" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="936" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="937" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="938" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="939" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="940" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="941" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="942" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="943" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="944" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="945" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="946" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="947" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="948" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="949" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="950" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="951" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="952" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="953" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="954" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="955" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="956" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="957" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="958" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="959" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="960" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="961" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="962" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="963" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="964" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="965" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="966" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="967" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="968" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="969" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="970" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="971" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="972" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="973" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="974" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="975" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="976" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="977" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="978" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="979" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="980" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="981" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="982" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="983" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="984" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="985" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="986" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="987" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="988" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="989" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="990" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="991" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="992" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="993" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="994" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="995" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="996" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="997" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="998" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="999" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1000" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1001" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1002" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1003" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1004" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1005" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1006" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1007" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1008" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1009" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1010" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1011" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1012" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1013" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1014" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1015" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1016" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1017" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1018" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1019" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1020" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1021" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1022" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1023" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1024" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1025" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1026" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1027" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1028" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1029" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1030" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1031" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1032" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1033" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1034" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1035" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1036" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1037" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1038" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1039" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1040" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1041" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1042" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1043" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1044" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1045" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1046" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1047" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1048" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1049" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1050" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1051" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1052" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1053" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1054" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1055" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1056" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1057" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1058" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1059" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1060" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1061" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1062" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1063" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1064" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1065" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1066" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1067" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1068" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1069" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1070" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1071" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1072" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1073" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1074" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1075" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1076" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1077" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1078" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1079" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1080" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1081" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1082" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1083" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1084" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1085" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1086" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1087" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1088" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1089" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1090" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1091" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1092" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1093" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1094" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1095" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1096" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1097" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1098" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1099" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1100" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1101" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1102" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1103" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1104" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1105" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1106" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1107" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1108" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1109" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1110" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1111" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1112" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1113" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1114" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1115" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1116" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1117" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1118" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1119" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1120" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1121" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1122" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1123" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1124" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1125" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1126" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1127" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1128" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1129" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1130" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1131" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1132" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1133" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1134" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1135" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1136" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1137" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1138" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1139" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1140" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1141" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1142" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1143" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1144" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1145" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1146" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1147" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1148" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1149" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1150" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1151" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1152" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1153" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1154" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1155" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1156" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1157" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1158" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1159" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1160" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1161" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1162" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1163" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1164" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1165" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1166" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1167" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1168" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1169" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1170" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1171" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1172" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1173" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1174" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1175" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1176" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1177" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1178" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1179" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1180" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1181" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1182" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1183" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1184" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1185" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1186" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1187" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1188" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1189" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1190" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1191" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1192" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1193" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1194" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1195" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1196" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1197" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1198" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1199" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1200" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1201" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1202" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1203" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1204" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1205" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1206" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1207" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1208" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1209" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1210" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1211" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1212" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1213" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1214" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1215" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1216" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1217" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1218" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1219" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1220" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1221" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1222" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1223" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1224" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1225" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1226" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1227" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1228" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1229" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1230" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1231" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1232" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1233" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1234" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1235" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1236" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1237" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1238" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1239" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1240" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1241" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1242" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1243" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1244" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1245" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1246" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1247" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1248" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1249" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1250" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1251" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1252" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1253" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1254" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1255" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1256" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1257" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1258" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1259" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1260" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1261" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1262" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1263" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1264" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1265" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1266" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1267" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1268" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1269" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1270" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1271" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1272" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1273" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1274" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1275" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1276" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1277" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1278" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1279" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1280" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1281" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1282" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1283" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1284" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1285" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1286" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1287" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1288" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1289" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1290" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1291" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1292" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1293" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1294" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1295" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1296" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1297" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1298" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1299" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1300" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1301" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1302" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1303" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1304" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1305" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1306" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1307" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1308" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1309" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1310" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1311" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1312" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1313" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1314" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1315" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1316" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1317" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1318" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1319" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1320" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1321" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1322" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1323" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1324" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1325" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1326" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1327" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1328" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1329" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1330" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1331" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1332" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1333" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1334" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1335" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1336" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1337" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1338" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1339" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1340" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1341" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1342" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1343" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1344" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1345" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1346" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1347" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1348" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1349" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1350" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1351" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1352" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1353" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1354" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1355" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1356" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1357" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1358" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1359" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1360" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1361" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1362" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1363" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1364" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1365" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1366" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1367" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1368" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1369" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1370" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1371" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1372" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1373" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1374" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1375" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1376" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1377" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1378" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1379" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1380" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1381" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1382" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1383" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1384" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1385" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1386" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1387" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1388" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1389" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1390" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1391" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1392" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1393" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1394" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1395" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1396" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1397" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1398" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1399" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1400" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1401" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1402" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1403" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1404" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1405" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1406" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1407" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1408" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1409" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1410" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1411" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1412" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1413" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1414" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1415" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1416" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1417" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1418" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1419" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1420" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1421" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1422" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1423" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1424" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1425" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1426" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1427" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1428" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1429" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1430" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1431" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1432" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1433" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1434" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1435" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1436" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1437" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1438" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1439" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1440" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1441" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1442" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1443" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1444" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1445" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1446" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1447" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1448" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1449" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1450" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1451" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1452" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1453" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1454" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1455" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1456" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1457" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1458" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1459" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1460" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1461" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1462" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1463" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1464" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1465" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1466" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1467" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1468" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1469" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1470" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1471" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1472" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1473" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1474" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1475" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1476" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1477" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1478" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1479" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1480" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1481" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1482" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1483" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1484" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1485" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1486" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1487" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1488" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1489" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1490" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1491" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1492" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1493" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1494" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1495" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1496" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1497" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1498" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1499" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1500" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1501" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1502" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1503" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1504" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1505" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1506" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1507" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1508" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1509" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1510" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1511" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1512" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1513" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1514" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1515" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1516" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1517" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1518" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1519" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1520" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1521" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1522" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1523" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1524" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1525" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1526" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1527" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1528" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1529" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1530" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1531" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1532" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1533" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1534" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1535" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1536" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1537" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1538" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1539" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1540" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1541" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1542" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1543" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1544" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1545" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1546" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1547" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1548" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1549" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1550" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1551" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1552" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1553" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1554" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1555" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1556" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1557" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1558" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1559" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1560" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1561" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1562" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1563" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1564" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1565" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1566" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1567" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1568" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1569" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1570" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1571" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1572" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1573" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1574" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1575" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1576" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1577" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1578" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1579" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1580" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1581" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1582" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1583" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1584" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1585" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1586" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1587" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1588" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1589" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1590" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1591" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1592" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1593" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1594" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1595" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1596" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1597" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1598" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1599" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1600" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1601" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1602" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1603" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1604" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1605" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1606" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1607" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1608" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1609" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1610" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1611" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1612" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1613" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1614" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1615" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1616" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1617" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1618" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1619" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1620" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1621" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1622" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1623" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1624" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1625" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1626" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1627" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1628" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1629" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1630" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1631" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1632" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1633" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1634" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1635" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1636" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1637" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1638" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1639" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1640" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1641" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1642" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1643" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1644" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1645" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1646" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1647" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1648" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1649" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1650" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1651" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1652" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1653" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1654" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1655" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1656" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1657" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1658" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1659" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1660" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1661" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1662" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1663" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1664" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1665" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1666" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1667" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1668" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1669" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1670" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1671" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1672" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1673" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1674" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1675" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1676" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1677" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1678" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1679" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1680" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1681" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1682" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1683" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1684" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1685" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1686" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1687" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1688" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1689" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1690" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1691" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1692" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1693" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1694" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1695" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1696" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1697" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1698" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1699" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1700" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1701" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1702" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1703" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1704" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1705" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1706" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1707" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1708" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1709" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1710" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1711" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1712" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1713" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1714" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1715" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1716" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1717" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1718" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1719" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1720" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1721" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1722" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1723" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1724" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1725" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1726" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1727" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1728" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1729" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1730" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1731" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1732" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1733" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1734" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1735" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1736" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1737" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1738" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1739" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1740" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1741" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1742" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1743" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1744" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1745" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1746" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1747" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1748" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1749" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1750" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1751" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1752" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1753" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1754" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1755" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1756" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1757" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1758" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1759" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1760" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1761" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1762" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1763" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1764" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1765" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1766" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1767" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1768" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1769" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1770" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1771" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1772" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1773" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1774" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1775" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1776" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1777" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1778" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1779" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1780" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1781" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1782" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1783" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1784" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1785" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1786" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1787" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1788" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1789" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1790" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1791" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1792" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1793" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1794" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1795" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1796" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1797" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1798" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1799" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1800" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1801" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1802" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1803" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1804" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1805" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1806" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1807" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1808" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1809" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1810" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1811" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1812" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1813" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1814" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1815" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1816" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1817" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1818" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1819" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1820" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1821" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1822" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1823" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1824" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1825" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1826" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1827" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1828" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1829" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1830" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1831" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1832" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1833" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1834" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1835" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1836" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1837" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1838" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1839" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1840" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1841" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1842" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1843" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1844" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1845" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1846" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1847" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1848" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1849" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1850" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1851" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1852" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1853" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1854" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1855" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1856" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1857" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1858" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1859" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1860" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1861" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1862" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1863" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1864" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1865" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1866" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1867" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1868" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1869" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1870" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1871" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1872" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1873" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1874" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1875" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1876" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1877" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1878" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1879" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1880" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1881" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1882" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1883" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1884" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1885" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1886" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1887" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1888" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1889" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1890" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1891" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1892" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1893" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1894" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1895" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1896" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1897" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1898" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1899" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1900" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1901" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1902" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1903" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1904" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1905" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1906" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1907" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1908" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1909" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1910" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1911" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1912" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1913" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1914" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1915" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1916" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1917" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1918" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1919" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1920" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1921" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1922" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1923" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1924" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1925" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1926" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1927" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1928" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1929" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1930" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1931" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1932" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1933" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1934" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1935" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1936" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1937" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1938" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1939" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1940" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1941" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1942" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1943" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1944" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1945" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1946" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1947" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1948" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1949" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1950" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1951" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1952" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1953" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1954" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1955" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1956" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1957" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1958" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1959" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1960" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1961" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1962" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1963" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1964" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1965" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1966" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1967" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1968" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1969" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1970" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1971" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1972" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1973" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1974" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1975" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1976" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1977" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1978" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1979" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1980" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1981" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1982" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1983" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1984" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1985" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1986" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1987" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1988" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1989" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1990" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1991" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1992" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1993" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1994" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1995" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1996" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1997" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1998" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="1999" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2000" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2001" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2002" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2003" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2004" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2005" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2006" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2007" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2008" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2009" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2010" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2011" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2012" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2013" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2014" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2015" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="2016" s="26" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -46810,6 +45123,21 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEE962D7-88F5-4ECB-8EFE-9CC1E43161C7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C79A73C4-BC46-4B18-B928-2FD1523096DF}">
   <dimension ref="A1:B2013"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -52910,7 +51238,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B626D9F-AB7A-46FB-82DA-32B552A0F929}">
   <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -52973,7 +51301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{193BA57C-E611-4497-BF08-E3370EB34D71}">
   <dimension ref="A1:C115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -53251,7 +51579,7 @@
       </c>
       <c r="C29" s="28"/>
     </row>
-    <row r="30" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="28">
         <v>29</v>
       </c>
@@ -53278,7 +51606,7 @@
       </c>
       <c r="C32" s="28"/>
     </row>
-    <row r="33" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="28">
         <v>32</v>
       </c>
@@ -53323,7 +51651,7 @@
       </c>
       <c r="C37" s="28"/>
     </row>
-    <row r="38" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="28">
         <v>37</v>
       </c>
@@ -53368,7 +51696,7 @@
       </c>
       <c r="C42" s="28"/>
     </row>
-    <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="28">
         <v>42</v>
       </c>
@@ -53377,7 +51705,7 @@
       </c>
       <c r="C43" s="28"/>
     </row>
-    <row r="44" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="28">
         <v>43</v>
       </c>
@@ -53386,7 +51714,7 @@
       </c>
       <c r="C44" s="28"/>
     </row>
-    <row r="45" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="28">
         <v>44</v>
       </c>
@@ -53395,7 +51723,7 @@
       </c>
       <c r="C45" s="28"/>
     </row>
-    <row r="46" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="28">
         <v>45</v>
       </c>
@@ -53413,7 +51741,7 @@
       </c>
       <c r="C47" s="28"/>
     </row>
-    <row r="48" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="28">
         <v>47</v>
       </c>
@@ -53431,7 +51759,7 @@
       </c>
       <c r="C49" s="28"/>
     </row>
-    <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="28">
         <v>49</v>
       </c>
@@ -53449,7 +51777,7 @@
       </c>
       <c r="C51" s="28"/>
     </row>
-    <row r="52" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="28">
         <v>51</v>
       </c>
@@ -53485,7 +51813,7 @@
       </c>
       <c r="C55" s="28"/>
     </row>
-    <row r="56" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="28">
         <v>55</v>
       </c>
@@ -53494,7 +51822,7 @@
       </c>
       <c r="C56" s="28"/>
     </row>
-    <row r="57" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="28">
         <v>56</v>
       </c>
@@ -53512,7 +51840,7 @@
       </c>
       <c r="C58" s="28"/>
     </row>
-    <row r="59" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="28">
         <v>58</v>
       </c>
@@ -53548,7 +51876,7 @@
       </c>
       <c r="C62" s="28"/>
     </row>
-    <row r="63" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="28">
         <v>62</v>
       </c>
@@ -53559,7 +51887,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="28">
         <v>63</v>
       </c>
@@ -53570,7 +51898,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="28">
         <v>64</v>
       </c>
@@ -53592,7 +51920,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="28">
         <v>66</v>
       </c>
@@ -53625,7 +51953,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="28">
         <v>69</v>
       </c>
@@ -53636,7 +51964,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="28">
         <v>70</v>
       </c>
@@ -53669,7 +51997,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="28">
         <v>73</v>
       </c>
@@ -53680,7 +52008,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="28">
         <v>74</v>
       </c>
@@ -53691,7 +52019,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="28">
         <v>75</v>
       </c>
@@ -53713,7 +52041,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="28">
         <v>77</v>
       </c>
@@ -53735,7 +52063,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="28">
         <v>79</v>
       </c>
@@ -53757,7 +52085,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="28">
         <v>81</v>
       </c>
@@ -53768,7 +52096,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="28">
         <v>82</v>
       </c>
@@ -53779,7 +52107,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="28">
         <v>83</v>
       </c>
@@ -53790,7 +52118,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="28">
         <v>84</v>
       </c>
@@ -53834,7 +52162,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="28">
         <v>88</v>
       </c>
@@ -53867,7 +52195,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="28">
         <v>91</v>
       </c>
@@ -53889,7 +52217,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="28">
         <v>93</v>
       </c>
@@ -53900,7 +52228,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="28">
         <v>94</v>
       </c>
@@ -53944,7 +52272,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="28">
         <v>98</v>
       </c>
@@ -53955,7 +52283,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="28">
         <v>99</v>
       </c>
@@ -53966,7 +52294,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="28">
         <v>100</v>
       </c>
@@ -53988,7 +52316,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="28">
         <v>102</v>
       </c>
@@ -54010,7 +52338,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="28">
         <v>104</v>
       </c>
@@ -54054,7 +52382,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="28">
         <v>108</v>
       </c>
@@ -54065,7 +52393,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="28">
         <v>109</v>
       </c>
